--- a/repair/back/doc/estimate/detail.xlsx
+++ b/repair/back/doc/estimate/detail.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="Polaris Office Sheet" lastEdited="7" lowestEdited="7" rupBuild=""/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="30" windowWidth="25755" windowHeight="11595" tabRatio="731" activeTab="0"/>
+    <workbookView xWindow="360" yWindow="30" windowWidth="25755" windowHeight="11595" tabRatio="731" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="갑지" sheetId="21" r:id="rId1"/>
@@ -381,7 +381,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="445" uniqueCount="445">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="447">
   <si>
     <t>식</t>
   </si>
@@ -2484,6 +2484,12 @@
   <si>
     <t xml:space="preserve">다. 점 검 범 위  : </t>
   </si>
+  <si>
+    <t>「시설물의 안전 및 유지관리에 관한 특별법」(이하 “시설물안전법”이라 한다) 제11조, 제12조 및</t>
+  </si>
+  <si>
+    <t>동법 시행령 제8조에 따라</t>
+  </si>
 </sst>
 </file>
 
@@ -2563,7 +2569,7 @@
     <numFmt numFmtId="245" formatCode="0_ "/>
     <numFmt numFmtId="246" formatCode="yyyy&quot;년&quot;\ m&quot;월&quot;\ d&quot;일&quot;;@"/>
   </numFmts>
-  <fonts count="165">
+  <fonts count="173">
     <font>
       <sz val="11.0"/>
       <name val="돋움"/>
@@ -3412,16 +3418,6 @@
       <color rgb="FF000000"/>
     </font>
     <font>
-      <sz val="10.0"/>
-      <name val="돋움"/>
-      <color rgb="FF000000"/>
-    </font>
-    <font>
-      <sz val="11.0"/>
-      <name val="돋움"/>
-      <color rgb="FF000000"/>
-    </font>
-    <font>
       <b/>
       <sz val="19.0"/>
       <name val="함초롬바탕"/>
@@ -3459,6 +3455,62 @@
     <font>
       <b/>
       <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="16.0"/>
+      <name val="돋움"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10.0"/>
+      <name val="돋움"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <name val="돋움"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24.0"/>
+      <name val="바탕"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="19.0"/>
+      <name val="함초롬바탕"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="17.0"/>
+      <name val="맑은 고딕"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="36.0"/>
+      <name val="맑은 고딕"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18.0"/>
+      <name val="맑은 고딕"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="33.0"/>
+      <name val="맑은 고딕"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="2.0"/>
       <name val="맑은 고딕"/>
       <color rgb="FF000000"/>
     </font>
@@ -5022,7 +5074,6 @@
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left/>
@@ -5031,7 +5082,6 @@
       <bottom style="thick">
         <color theme="4"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left/>
@@ -5040,7 +5090,6 @@
       <bottom style="thick">
         <color rgb="FFACCCEA"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left/>
@@ -5049,7 +5098,6 @@
       <bottom style="medium">
         <color theme="4" tint="0.399980"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -5064,7 +5112,6 @@
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -5079,7 +5126,6 @@
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="double">
@@ -5094,7 +5140,6 @@
       <bottom style="double">
         <color rgb="FF3F3F3F"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left/>
@@ -5103,7 +5148,6 @@
       <bottom style="double">
         <color rgb="FFFF8001"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left/>
@@ -5114,7 +5158,6 @@
       <bottom style="double">
         <color theme="4"/>
       </bottom>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="3167">
@@ -14662,7 +14705,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="540">
+  <cellXfs count="546">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="3104">
       <alignment vertical="center"/>
@@ -16268,6 +16311,24 @@
     </xf>
     <xf numFmtId="0" fontId="112" fillId="0" borderId="96" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="90" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="90" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="90" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3168">
@@ -20520,7 +20581,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="B1:AG1591"/>
+  <dimension ref="B1:AF1591"/>
   <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="13.500000"/>
   <cols>
     <col min="1" max="1" style="64" width="8.78277800" customWidth="1" outlineLevel="0"/>
@@ -20529,11 +20590,10 @@
     <col min="11" max="29" style="64" width="3.33833334" customWidth="1" outlineLevel="0"/>
     <col min="30" max="30" style="64" width="2.33833334" customWidth="1" outlineLevel="0"/>
     <col min="31" max="257" style="64" width="6.78277800" customWidth="1" outlineLevel="0"/>
-    <col min="258" max="258" style="64" width="8.78277800" customWidth="1" outlineLevel="0"/>
-    <col min="259" max="16384" style="64" width="8.78277800" customWidth="1" outlineLevel="0"/>
+    <col min="258" max="16384" style="64" width="8.78277800" customWidth="1" outlineLevel="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:33" s="70" customFormat="1" ht="42.000000" customHeight="1">
+    <row r="1" spans="2:29" s="70" customFormat="1" ht="42.000000" customHeight="1">
       <c r="B1" s="361" t="s">
         <v>114</v>
       </c>
@@ -20565,7 +20625,7 @@
       <c r="AB1" s="361"/>
       <c r="AC1" s="361"/>
     </row>
-    <row r="2" spans="2:33" s="70" customFormat="1" ht="12.000000" customHeight="1">
+    <row r="2" spans="2:29" s="70" customFormat="1" ht="12.000000" customHeight="1">
       <c r="B2" s="209"/>
       <c r="C2" s="209"/>
       <c r="D2" s="209"/>
@@ -20595,7 +20655,7 @@
       <c r="AB2" s="210"/>
       <c r="AC2" s="210"/>
     </row>
-    <row r="3" spans="2:33" s="70" customFormat="1" ht="18.000000" customHeight="1">
+    <row r="3" spans="2:29" s="70" customFormat="1" ht="18.000000" customHeight="1">
       <c r="B3" s="362" t="s">
         <v>409</v>
       </c>
@@ -20627,7 +20687,7 @@
       <c r="AB3" s="362"/>
       <c r="AC3" s="362"/>
     </row>
-    <row r="4" spans="2:33" s="70" customFormat="1" ht="7.500000" customHeight="1">
+    <row r="4" spans="2:29" s="70" customFormat="1" ht="7.500000" customHeight="1">
       <c r="B4" s="211"/>
       <c r="C4" s="211"/>
       <c r="D4" s="211"/>
@@ -20657,7 +20717,7 @@
       <c r="AB4" s="212"/>
       <c r="AC4" s="212"/>
     </row>
-    <row r="5" spans="2:33" s="70" customFormat="1" ht="5.000000" customHeight="1">
+    <row r="5" spans="2:29" s="70" customFormat="1" ht="5.000000" customHeight="1">
       <c r="B5" s="209"/>
       <c r="C5" s="209"/>
       <c r="D5" s="209"/>
@@ -20687,7 +20747,7 @@
       <c r="AB5" s="210"/>
       <c r="AC5" s="210"/>
     </row>
-    <row r="6" spans="2:33" s="70" customFormat="1" ht="20.000000" customHeight="1">
+    <row r="6" spans="2:29" s="70" customFormat="1" ht="20.000000" customHeight="1">
       <c r="B6" s="360" t="s">
         <v>113</v>
       </c>
@@ -20721,7 +20781,7 @@
       <c r="AB6" s="209"/>
       <c r="AC6" s="209"/>
     </row>
-    <row r="7" spans="2:33" s="70" customFormat="1" ht="20.000000" customHeight="1">
+    <row r="7" spans="2:29" s="70" customFormat="1" ht="20.000000" customHeight="1">
       <c r="B7" s="360" t="s">
         <v>111</v>
       </c>
@@ -20755,7 +20815,7 @@
       <c r="AB7" s="209"/>
       <c r="AC7" s="209"/>
     </row>
-    <row r="8" spans="2:33" s="70" customFormat="1" ht="20.000000" customHeight="1">
+    <row r="8" spans="2:29" s="70" customFormat="1" ht="20.000000" customHeight="1">
       <c r="B8" s="360" t="s">
         <v>110</v>
       </c>
@@ -20789,7 +20849,7 @@
       <c r="AB8" s="213"/>
       <c r="AC8" s="213"/>
     </row>
-    <row r="9" spans="2:33" s="70" customFormat="1" ht="20.000000" customHeight="1">
+    <row r="9" spans="2:29" s="70" customFormat="1" ht="20.000000" customHeight="1">
       <c r="B9" s="360" t="s">
         <v>109</v>
       </c>
@@ -20802,32 +20862,8 @@
       <c r="G9" s="209"/>
       <c r="H9" s="209"/>
       <c r="I9" s="209"/>
-      <c r="J9" s="70"/>
-      <c r="K9" s="70"/>
-      <c r="L9" s="70"/>
-      <c r="M9" s="70"/>
-      <c r="N9" s="70"/>
-      <c r="O9" s="70"/>
-      <c r="P9" s="70"/>
-      <c r="Q9" s="70"/>
-      <c r="R9" s="70"/>
-      <c r="S9" s="70"/>
-      <c r="T9" s="70"/>
-      <c r="U9" s="70"/>
-      <c r="V9" s="70"/>
-      <c r="W9" s="70"/>
-      <c r="X9" s="70"/>
-      <c r="Y9" s="70"/>
-      <c r="Z9" s="70"/>
-      <c r="AA9" s="70"/>
-      <c r="AB9" s="70"/>
-      <c r="AC9" s="70"/>
-      <c r="AD9" s="70"/>
-      <c r="AE9" s="70"/>
-      <c r="AF9" s="70"/>
-      <c r="AG9" s="70"/>
-    </row>
-    <row r="10" spans="2:33" s="70" customFormat="1" ht="20.000000" customHeight="1">
+    </row>
+    <row r="10" spans="2:29" s="70" customFormat="1" ht="20.000000" customHeight="1">
       <c r="B10" s="360" t="s">
         <v>107</v>
       </c>
@@ -20861,7 +20897,7 @@
       <c r="AB10" s="213"/>
       <c r="AC10" s="213"/>
     </row>
-    <row r="11" spans="2:33" s="70" customFormat="1" ht="13.500000" hidden="1" customHeight="1">
+    <row r="11" spans="2:29" s="70" customFormat="1" ht="13.500000" hidden="1" customHeight="1">
       <c r="B11" s="214"/>
       <c r="C11" s="214"/>
       <c r="D11" s="214"/>
@@ -20891,7 +20927,7 @@
       <c r="AB11" s="214"/>
       <c r="AC11" s="214"/>
     </row>
-    <row r="12" spans="2:33" s="70" customFormat="1" ht="7.500000" customHeight="1">
+    <row r="12" spans="2:29" s="70" customFormat="1" ht="7.500000" customHeight="1">
       <c r="B12" s="211"/>
       <c r="C12" s="211"/>
       <c r="D12" s="211"/>
@@ -20921,7 +20957,7 @@
       <c r="AB12" s="211"/>
       <c r="AC12" s="211"/>
     </row>
-    <row r="13" spans="2:33" s="70" customFormat="1" ht="5.000000" customHeight="1">
+    <row r="13" spans="2:29" s="70" customFormat="1" ht="5.000000" customHeight="1">
       <c r="B13" s="209"/>
       <c r="C13" s="209"/>
       <c r="D13" s="209"/>
@@ -20951,7 +20987,7 @@
       <c r="AB13" s="209"/>
       <c r="AC13" s="209"/>
     </row>
-    <row r="14" spans="2:33" s="70" customFormat="1" ht="20.000000" customHeight="1">
+    <row r="14" spans="2:29" s="70" customFormat="1" ht="20.000000" customHeight="1">
       <c r="B14" s="213" t="s">
         <v>426</v>
       </c>
@@ -20983,7 +21019,7 @@
       <c r="AB14" s="213"/>
       <c r="AC14" s="213"/>
     </row>
-    <row r="15" spans="2:33" s="70" customFormat="1" ht="10.000000" customHeight="1">
+    <row r="15" spans="2:29" s="70" customFormat="1" ht="10.000000" customHeight="1">
       <c r="B15" s="209"/>
       <c r="C15" s="209"/>
       <c r="D15" s="209"/>
@@ -21013,7 +21049,7 @@
       <c r="AB15" s="209"/>
       <c r="AC15" s="209"/>
     </row>
-    <row r="16" spans="2:33" s="70" customFormat="1" ht="72.000000" customHeight="1">
+    <row r="16" spans="2:29" s="70" customFormat="1" ht="72.000000" customHeight="1">
       <c r="B16" s="215" t="s">
         <v>427</v>
       </c>
@@ -35801,10 +35837,10 @@
     <mergeCell ref="B20:K20"/>
     <mergeCell ref="F21:K21"/>
     <mergeCell ref="L21:AC21"/>
+    <mergeCell ref="F22:K22"/>
+    <mergeCell ref="L22:AC22"/>
     <mergeCell ref="F23:K23"/>
     <mergeCell ref="L23:AC23"/>
-    <mergeCell ref="F22:K22"/>
-    <mergeCell ref="L22:AC22"/>
     <mergeCell ref="F24:K24"/>
     <mergeCell ref="L24:AC24"/>
     <mergeCell ref="F25:K25"/>
@@ -35843,8 +35879,7 @@
     <col min="8" max="8" style="130" width="12.78277800" customWidth="1" outlineLevel="0"/>
     <col min="9" max="9" style="132" width="14.78277800" customWidth="1" outlineLevel="0"/>
     <col min="10" max="256" style="130" width="8.78277800" customWidth="1" outlineLevel="0"/>
-    <col min="257" max="257" style="130" width="11.44944403" customWidth="1" outlineLevel="0"/>
-    <col min="258" max="16384" style="130" width="11.44944403" customWidth="1" outlineLevel="0"/>
+    <col min="257" max="16384" style="130" width="11.44944403" customWidth="1" outlineLevel="0"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:9" s="1" customFormat="1" ht="39.000000" customHeight="1">
@@ -35904,9 +35939,9 @@
         <v>121</v>
       </c>
       <c r="C5" s="394"/>
-      <c r="D5" s="395" t="e">
+      <c r="D5" s="395">
         <f>"일금 "&amp;NUMBERSTRING(H30,1)&amp;"원정"&amp;TEXT(H30,"(￦ #,##0)")&amp;" "</f>
-        <v>일금 #VALUE!원정</v>
+        <v/>
       </c>
       <c r="E5" s="396"/>
       <c r="F5" s="396"/>
@@ -38022,7 +38057,7 @@
     </row>
     <row r="59" spans="2:21" ht="24.950000" customHeight="1">
       <c r="B59" s="292" t="s">
-        <v>421</v>
+        <v>445</v>
       </c>
       <c r="C59" s="292"/>
       <c r="D59" s="292"/>
@@ -38045,25 +38080,25 @@
       <c r="U59" s="292"/>
     </row>
     <row r="60" spans="2:21" ht="24.950000" customHeight="1">
-      <c r="B60" s="23" t="s">
-        <v>422</v>
-      </c>
-      <c r="C60" s="23"/>
-      <c r="D60" s="23"/>
-      <c r="E60" s="23"/>
-      <c r="F60" s="23"/>
-      <c r="G60" s="23"/>
-      <c r="H60" s="23"/>
-      <c r="I60" s="23"/>
-      <c r="J60" s="301" t="str">
+      <c r="B60" s="542" t="s">
+        <v>446</v>
+      </c>
+      <c r="C60" s="542"/>
+      <c r="D60" s="542"/>
+      <c r="E60" s="542"/>
+      <c r="F60" s="542"/>
+      <c r="G60" s="542"/>
+      <c r="H60" s="542"/>
+      <c r="I60" s="545" t="str">
         <f>B9</f>
         <v>효성뉴서울5차아파트</v>
       </c>
-      <c r="K60" s="301"/>
-      <c r="L60" s="301"/>
-      <c r="M60" s="301"/>
-      <c r="N60" s="301"/>
-      <c r="O60" s="301"/>
+      <c r="J60" s="545"/>
+      <c r="K60" s="545"/>
+      <c r="L60" s="545"/>
+      <c r="M60" s="545"/>
+      <c r="N60" s="545"/>
+      <c r="O60" s="545"/>
       <c r="P60" s="23" t="s">
         <v>423</v>
       </c>
@@ -38200,7 +38235,7 @@
     </row>
     <row r="68" spans="2:21" ht="24.950000" customHeight="1">
       <c r="C68" s="30" t="str">
-        <f>"② 위      치 : "&amp;E54</f>
+        <f>"② 위      치 : "&amp;갑지!L22</f>
         <v>② 위      치 : 인천 계양구 아나지로 199 (효성동)</v>
       </c>
       <c r="D68" s="30"/>
@@ -40405,8 +40440,8 @@
     <mergeCell ref="B56:U56"/>
     <mergeCell ref="B57:U57"/>
     <mergeCell ref="B59:U59"/>
-    <mergeCell ref="B60:I60"/>
-    <mergeCell ref="J60:O60"/>
+    <mergeCell ref="B60:H60"/>
+    <mergeCell ref="I60:O60"/>
     <mergeCell ref="P60:U60"/>
     <mergeCell ref="B61:U61"/>
     <mergeCell ref="B63:J63"/>
@@ -40577,8 +40612,7 @@
   <cols>
     <col min="1" max="1" style="138" width="12.33833334" customWidth="1" outlineLevel="0"/>
     <col min="2" max="16" style="138" width="4.33833334" customWidth="1" outlineLevel="0"/>
-    <col min="17" max="17" style="138" width="8.78277800" customWidth="1" outlineLevel="0"/>
-    <col min="18" max="16384" style="138" width="8.78277800" customWidth="1" outlineLevel="0"/>
+    <col min="17" max="16384" style="138" width="8.78277800" customWidth="1" outlineLevel="0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="19.500000" customHeight="1">
@@ -41729,8 +41763,7 @@
   <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="16.500000"/>
   <cols>
     <col min="1" max="1" style="138" width="111.78277418" customWidth="1" outlineLevel="0"/>
-    <col min="2" max="2" style="138" width="8.78277800" customWidth="1" outlineLevel="0"/>
-    <col min="3" max="16384" style="138" width="8.78277800" customWidth="1" outlineLevel="0"/>
+    <col min="2" max="16384" style="138" width="8.78277800" customWidth="1" outlineLevel="0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" ht="204.000000" customHeight="1">

--- a/repair/back/doc/estimate/detail.xlsx
+++ b/repair/back/doc/estimate/detail.xlsx
@@ -2569,7 +2569,7 @@
     <numFmt numFmtId="245" formatCode="0_ "/>
     <numFmt numFmtId="246" formatCode="yyyy&quot;년&quot;\ m&quot;월&quot;\ d&quot;일&quot;;@"/>
   </numFmts>
-  <fonts count="173">
+  <fonts count="179">
     <font>
       <sz val="11.0"/>
       <name val="돋움"/>
@@ -3459,6 +3459,35 @@
       <color rgb="FF000000"/>
     </font>
     <font>
+      <b/>
+      <sz val="17.0"/>
+      <name val="맑은 고딕"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="36.0"/>
+      <name val="맑은 고딕"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18.0"/>
+      <name val="맑은 고딕"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="33.0"/>
+      <name val="맑은 고딕"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="2.0"/>
+      <name val="맑은 고딕"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
       <sz val="16.0"/>
       <name val="돋움"/>
       <color rgb="FF000000"/>
@@ -3487,30 +3516,32 @@
     </font>
     <font>
       <b/>
-      <sz val="17.0"/>
+      <sz val="20.0"/>
       <name val="맑은 고딕"/>
       <color rgb="FF000000"/>
     </font>
     <font>
-      <b/>
-      <sz val="36.0"/>
+      <sz val="26.0"/>
       <name val="맑은 고딕"/>
       <color rgb="FF000000"/>
     </font>
     <font>
-      <b/>
-      <sz val="18.0"/>
+      <sz val="14.0"/>
       <name val="맑은 고딕"/>
       <color rgb="FF000000"/>
     </font>
     <font>
-      <b/>
-      <sz val="33.0"/>
+      <sz val="20.0"/>
       <name val="맑은 고딕"/>
       <color rgb="FF000000"/>
     </font>
     <font>
-      <sz val="2.0"/>
+      <sz val="9.0"/>
+      <name val="맑은 고딕"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="16.0"/>
       <name val="맑은 고딕"/>
       <color rgb="FF000000"/>
     </font>
@@ -36550,8 +36581,8 @@
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.30" footer="0.30"/>
   <pageSetup paperSize="9" scale="90" orientation="portrait"/>
   <colBreaks count="2" manualBreakCount="2">
+    <brk id="9" max="35" man="1"/>
     <brk id="9" max="1048575" man="1"/>
-    <brk id="9" max="35" man="1"/>
   </colBreaks>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -39977,8 +40008,8 @@
       </c>
       <c r="Q150" s="47"/>
       <c r="R150" s="246">
-        <f>R141*P150%</f>
-        <v>132814.5</v>
+        <f>ROUND(R141*P150%,0)</f>
+        <v>132815</v>
       </c>
       <c r="S150" s="246"/>
       <c r="T150" s="246"/>
@@ -40011,8 +40042,8 @@
       </c>
       <c r="Q151" s="48"/>
       <c r="R151" s="240">
-        <f>(R141+R150)*P151%</f>
-        <v>146095.95</v>
+        <f>ROUND((R141+R150)*P151%,0)</f>
+        <v>146096</v>
       </c>
       <c r="S151" s="240"/>
       <c r="T151" s="240"/>
@@ -40038,8 +40069,8 @@
       <c r="P152" s="2"/>
       <c r="Q152" s="2"/>
       <c r="R152" s="250">
-        <f>R158+R157+R156+R155+R154</f>
-        <v>231041.55</v>
+        <f>INT(R158+R157+R156+R155+R154)</f>
+        <v>231041</v>
       </c>
       <c r="S152" s="250"/>
       <c r="T152" s="250"/>

--- a/repair/back/doc/estimate/detail.xlsx
+++ b/repair/back/doc/estimate/detail.xlsx
@@ -381,7 +381,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="447">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="482">
   <si>
     <t>식</t>
   </si>
@@ -2489,6 +2489,218 @@
   </si>
   <si>
     <t>동법 시행령 제8조에 따라</t>
+  </si>
+  <si>
+    <t>선택과업(필요시)</t>
+  </si>
+  <si>
+    <t>선   택   과   업   (   필   요   시   )</t>
+  </si>
+  <si>
+    <t>선   택   과   업   (  필   요   시  )</t>
+  </si>
+  <si>
+    <t>선   택   과   업  (  필   요   시  )</t>
+  </si>
+  <si>
+    <t>자료수집</t>
+  </si>
+  <si>
+    <t>자료수집
+및
+분석</t>
+  </si>
+  <si>
+    <t>현장조사 및 시험</t>
+  </si>
+  <si>
+    <t>안전성평가</t>
+  </si>
+  <si>
+    <t>종합평가</t>
+  </si>
+  <si>
+    <t>보수</t>
+  </si>
+  <si>
+    <t>보수·보강 방법</t>
+  </si>
+  <si>
+    <t>보고서</t>
+  </si>
+  <si>
+    <t>◦ 준공도면, 구조계산서, 특별시방서, 수리수문 계산서
+시공공보수 보강도면, 제작 및 작업도면면계측자료</t>
+  </si>
+  <si>
+    <t>◦ 준공도면, 구조계산서, 특별시방서, 수리수문 계산서
+시공·보수 보강도면, 제작 및 작업도면
+재료증명서, 품질시험기록, 재하시험 자료, 계측 자료
+시설물관리대장
+기존 안전점검·정밀안전진단 실시결과 검토분석
+보수·보강이력 검토·분석</t>
+  </si>
+  <si>
+    <t>◦ 준공도면, 구조계산서, 특별시방서, 수리수문 계산서
+◦시공·보수 보강도면, 제작 및 작업도면
+◦재료증명서, 품질시험기록, 재하시험 자료, 계측 자료
+◦시설물관리대장
+◦기존 안전점검·정밀안전진단 실시결과 검토분석
+◦보수·보강이력 검토·분석</t>
+  </si>
+  <si>
+    <t>◦ 기본시설물 또는 주요부재의 외관조사 및 외관조사망도 작성
+- 콘크리트 구조물 : 균열, 누수, 박리, 박락, 층분리, 백태, 철근노출 등
+- 강재 구조물</t>
+  </si>
+  <si>
+    <t>◦ 기본시설물 또는 주요부재의 외관조사 및 외관조사망도 작성
+- 콘크리트 구조물 : 균열, 누수, 박리, 박락, 층분리, 백태, 철근노출 등
+- 강재 구조물 : 균열, 도장상태, 부식상태 등</t>
+  </si>
+  <si>
+    <t>선  택  과  업  (  필  요  시  )</t>
+  </si>
+  <si>
+    <t>◦ 준공도면, 구조계산서, 특별시방서, 수리수문
+    계산서
+◦시공·보수 보강도면, 제작 및 작업도면
+◦재료증명서, 품질시험기록, 재하시험 자료,
+   계측 자료
+◦시설물관리대장
+◦기존 안전점검·정밀안전진단 실시결과 검토분석
+◦보수·보강이력 검토·분석</t>
+  </si>
+  <si>
+    <t>◦ 기본시설물 또는 주요부재의 외관조사 및 외관조사
+    망도 작성
+- 콘크리트 구조물 : 균열, 누수, 박리, 박락, 층분리, 
+   백태, 철근노출 등
+- 강재 구조물 : 균열, 도장상태, 부식상태 등</t>
+  </si>
+  <si>
+    <t>◦ 기본시설물 또는 주요부재의 외관조사 및 외관조사
+    망도 작성
+  - 콘크리트 구조물 : 균열, 누수, 박리, 박락, 층분리,
+    백태, 철근노출 등
+  - 강재 구조물 : 균열, 도장상태, 부식상태 등
+◦ 간단한 현장 재료시험 등</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ◦ 준공도면, 구조계산서, 특별시방서, 수리수문
+     계산서
+ ◦ 시공·보수 보강도면, 제작 및 작업도면
+ ◦ 재료증명서, 품질시험기록, 재하시험 자료,
+     계측 자료
+ ◦ 시설물관리대장
+◦ 기존 안전점검·정밀안전진단 실시결과 검토분석
+◦ 보수·보강이력 검토·분석</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ◦ 준공도면, 구조계산서, 특별시방서, 수리수문
+     계산서
+ ◦ 시공·보수 보강도면, 제작 및 작업도면
+ ◦ 재료증명서, 품질시험기록, 재하시험 자료,
+     계측 자료
+ ◦ 시설물관리대장
+ ◦ 기존 안전점검·정밀안전진단 실시결과 검토분석
+ ◦ 보수·보강이력 검토·분석</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ◦ 기본시설물 또는 주요부재의 외관조사 및 외관조
+     사망도 작성
+     - 콘크리트 구조물 : 균열, 누수, 박리, 박락, 층분
+        리, 백태, 철근노출 등
+     - 강재 구조물 : 균열, 도장상태, 부식상태 등
+ ◦ 간단한 현장 재료시험 등
+     - 콘크리트 비파괴 강도시험(반발강도시험)
+     - 콘크리트 중성화 시험
+     - 시험물(부재) 변위측정</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ◦ 외관조사 결과분석
+ ◦ 현장 재료시험 결과 분석
+ ◦ 대상 시설물(부재)에 대한 상태평가
+ ◦ 시설물 전체의 상대평가 결과에 대한 책임
+     기술자의 소견(안전등급 지정)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ◦ 시설물의 종합평가 결과에 대한 소견</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ◦ 보수</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ◦ 기본시설물 또는 주요부재의 외관조사 및 외관조
+     사망도 작성
+     - 콘크리트 구조물 : 균열, 누수, 박리, 박락, 층분
+       리, 백태, 철근노출 등
+     - 강재 구조물 : 균열, 도장상태, 부식상태 등
+ ◦ 간단한 현장 재료시험 등
+     - 콘크리트 비파괴 강도시험(반발강도시험)
+     - 콘크리트 중성화 시험
+     - 시험물(부재) 변위측정</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ◦ 보수·보강 방법 제시</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ◦ 시설물의 종합평가 결과에 대한 소견
+ ◦ 안전등급 지정</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+ ◦ 준공도면, 구조계산서, 특별시방서, 수리수문
+     계산서
+ ◦ 시공·보수 보강도면, 제작 및 작업도면
+ ◦ 재료증명서, 품질시험기록, 재하시험 자료,
+     계측 자료
+ ◦ 시설물관리대장
+ ◦ 기존 안전점검·정밀안전진단 실시결과 검토분석
+ ◦ 보수·보강이력 검토·분석
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+자료수집
+및
+분석
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 
+◦ 기본시설물 또는 주요부재의 외관조사 및 외관조
+     사망도 작성
+     - 콘크리트 구조물 : 균열, 누수, 박리, 박락, 층분
+       리, 백태, 철근노출 등
+     - 강재 구조물 : 균열, 도장상태, 부식상태 등
+ ◦ 간단한 현장 재료시험 등
+     - 콘크리트 비파괴 강도시험(반발강도시험)
+     - 콘크리트 중성화 시험
+     - 시험물(부재) 변위측정
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 
+ ◦ 기본시설물 또는 주요부재의 외관조사 및 외관조
+     사망도 작성
+     - 콘크리트 구조물 : 균열, 누수, 박리, 박락, 층분
+       리, 백태, 철근노출 등
+     - 강재 구조물 : 균열, 도장상태, 부식상태 등
+ ◦ 간단한 현장 재료시험 등
+     - 콘크리트 비파괴 강도시험(반발강도시험)
+     - 콘크리트 중성화 시험
+     - 시험물(부재) 변위측정
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 
+ ◦ 외관조사 결과분석
+ ◦ 현장 재료시험 결과 분석
+ ◦ 대상 시설물(부재)에 대한 상태평가
+ ◦ 시설물 전체의 상대평가 결과에 대한 책임
+     기술자의 소견(안전등급 지정)
+</t>
   </si>
 </sst>
 </file>
@@ -2569,7 +2781,7 @@
     <numFmt numFmtId="245" formatCode="0_ "/>
     <numFmt numFmtId="246" formatCode="yyyy&quot;년&quot;\ m&quot;월&quot;\ d&quot;일&quot;;@"/>
   </numFmts>
-  <fonts count="179">
+  <fonts count="180">
     <font>
       <sz val="11.0"/>
       <name val="돋움"/>
@@ -3488,33 +3700,6 @@
       <color rgb="FF000000"/>
     </font>
     <font>
-      <sz val="16.0"/>
-      <name val="돋움"/>
-      <color rgb="FF000000"/>
-    </font>
-    <font>
-      <sz val="10.0"/>
-      <name val="돋움"/>
-      <color rgb="FF000000"/>
-    </font>
-    <font>
-      <sz val="11.0"/>
-      <name val="돋움"/>
-      <color rgb="FF000000"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="24.0"/>
-      <name val="바탕"/>
-      <color rgb="FF000000"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="19.0"/>
-      <name val="함초롬바탕"/>
-      <color rgb="FF000000"/>
-    </font>
-    <font>
       <b/>
       <sz val="20.0"/>
       <name val="맑은 고딕"/>
@@ -3544,6 +3729,38 @@
       <sz val="16.0"/>
       <name val="맑은 고딕"/>
       <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="16.0"/>
+      <name val="돋움"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10.0"/>
+      <name val="돋움"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <name val="돋움"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24.0"/>
+      <name val="바탕"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="19.0"/>
+      <name val="함초롬바탕"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10.0"/>
+      <name val="돋움"/>
+      <color/>
     </font>
   </fonts>
   <fills count="45">
@@ -3815,7 +4032,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="122">
+  <borders count="128">
     <border>
       <left/>
       <right/>
@@ -5190,6 +5407,65 @@
         <color theme="4"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="3167">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -14736,7 +15012,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="546">
+  <cellXfs count="801">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="3104">
       <alignment vertical="center"/>
@@ -16360,6 +16636,769 @@
     </xf>
     <xf numFmtId="0" fontId="90" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="65" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="66" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="67" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="65" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="66" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="67" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="66" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="67" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="65" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="63" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="68" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="69" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="70" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="71" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="62" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="72" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="73" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="74" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="72" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="73" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="74" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="63" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="68" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="69" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="70" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="71" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="62" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="63" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="68" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="69" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="70" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="72" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="73" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="74" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="57" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="57" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="90" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="88" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="89" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="99" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="69" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="96" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="95" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="98" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="99" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="96" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="95" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="59" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="98" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="71" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="68" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="69" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="96" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="95" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="71" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="66" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="60" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="96" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="95" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="62" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="66" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="60" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="66" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="60" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="66" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="179" fillId="0" borderId="122" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="122" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="123" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="124" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="125" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="126" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="125" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="126" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="127" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="99" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="69" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="96" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="95" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="98" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="72" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="73" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="99" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="distributed" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="69" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="distributed" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="96" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="distributed" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="68" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="distributed" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="69" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="distributed" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="distributed" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="distributed" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="95" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="distributed" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="distributed" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="distributed" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="98" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="distributed" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="distributed" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="distributed" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="71" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="distributed" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="distributed" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="distributed" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="distributed" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="69" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="distributed" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="96" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="distributed" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="99" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="distributed" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="69" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="distributed" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="96" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="distributed" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="distributed" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="distributed" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="95" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="distributed" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="98" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="distributed" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="distributed" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="distributed" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="90" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="distributed" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="distributed" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="distributed" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="distributed" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="distributed" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="88" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="distributed" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="73" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="distributed" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="89" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="distributed" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="72" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="distributed" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="73" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="distributed" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="99" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="69" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="96" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="68" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="95" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="98" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="71" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="69" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="96" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="99" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="69" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="96" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="95" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="98" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="90" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="88" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="73" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="89" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="72" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="99" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="69" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="96" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="99" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="69" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="96" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="95" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="98" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="90" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="88" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="89" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="99" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="justify" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="69" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="justify" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="96" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="justify" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="68" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="justify" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="69" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="justify" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="justify" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="justify" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="95" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="justify" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="justify" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="justify" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="98" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="justify" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="justify" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="justify" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="71" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="justify" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="justify" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="justify" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="justify" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="69" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="justify" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="96" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="justify" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="99" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="justify" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="69" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="justify" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="96" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="justify" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="justify" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="justify" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="95" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="justify" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="98" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="justify" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="justify" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="justify" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="90" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="justify" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="justify" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="justify" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="justify" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="justify" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="88" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="justify" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="73" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="justify" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="89" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="justify" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="72" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="justify" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="73" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="justify" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3168">
@@ -36581,8 +37620,8 @@
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.30" footer="0.30"/>
   <pageSetup paperSize="9" scale="90" orientation="portrait"/>
   <colBreaks count="2" manualBreakCount="2">
+    <brk id="9" max="1048575" man="1"/>
     <brk id="9" max="35" man="1"/>
-    <brk id="9" max="1048575" man="1"/>
   </colBreaks>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -36593,7 +37632,7 @@
   <sheetPr>
     <tabColor rgb="92d050"/>
   </sheetPr>
-  <dimension ref="B1:AUT172"/>
+  <dimension ref="B1:AUT164"/>
   <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="13.500000"/>
   <cols>
     <col min="2" max="6" width="4.44944451" customWidth="1" outlineLevel="0"/>
@@ -39075,13 +40114,13 @@
       <c r="T112" s="30"/>
       <c r="U112" s="30"/>
     </row>
-    <row r="113" spans="2:21" ht="20.000000" customHeight="1">
+    <row r="113" spans="2:22" ht="20.000000" customHeight="1">
       <c r="B113" s="28"/>
       <c r="F113" s="5"/>
       <c r="G113" s="19"/>
       <c r="I113" s="4"/>
     </row>
-    <row r="114" spans="2:21" ht="20.000000" customHeight="1">
+    <row r="114" spans="2:22" ht="20.000000" customHeight="1">
       <c r="B114" s="221" t="s">
         <v>399</v>
       </c>
@@ -39094,7 +40133,7 @@
       <c r="I114" s="30"/>
       <c r="J114" s="30"/>
     </row>
-    <row r="115" spans="2:21" ht="40.000000" customHeight="1">
+    <row r="115" spans="2:22" ht="40.000000" customHeight="1">
       <c r="C115" s="22" t="s">
         <v>64</v>
       </c>
@@ -39117,13 +40156,13 @@
       <c r="T115" s="22"/>
       <c r="U115" s="22"/>
     </row>
-    <row r="116" spans="2:21" ht="20.000000" customHeight="1">
+    <row r="116" spans="2:22" ht="20.000000" customHeight="1">
       <c r="B116" s="28"/>
       <c r="F116" s="5"/>
       <c r="G116" s="19"/>
       <c r="I116" s="4"/>
     </row>
-    <row r="117" spans="2:21" ht="20.000000" customHeight="1">
+    <row r="117" spans="2:22" ht="20.000000" customHeight="1">
       <c r="B117" s="221" t="s">
         <v>400</v>
       </c>
@@ -39136,7 +40175,7 @@
       <c r="I117" s="221"/>
       <c r="J117" s="221"/>
     </row>
-    <row r="118" spans="2:21" ht="124.000000" customHeight="1">
+    <row r="118" spans="2:22" ht="124.000000" customHeight="1">
       <c r="C118" s="293" t="s">
         <v>65</v>
       </c>
@@ -39160,7 +40199,7 @@
       <c r="U118" s="293"/>
     </row>
     <row r="119" ht="409.500000" customHeight="1"/>
-    <row r="120" spans="2:21" ht="16.500000" customHeight="1">
+    <row r="120" spans="2:22" ht="16.500000" customHeight="1">
       <c r="B120" s="270" t="s">
         <v>66</v>
       </c>
@@ -39172,7 +40211,7 @@
       <c r="H120" s="270"/>
       <c r="I120" s="270"/>
     </row>
-    <row r="121" spans="2:21" ht="33.750000" customHeight="1">
+    <row r="121" spans="2:22" ht="33.750000" customHeight="1">
       <c r="B121" s="271" t="s">
         <v>67</v>
       </c>
@@ -39196,423 +40235,428 @@
       <c r="T121" s="271"/>
       <c r="U121" s="271"/>
     </row>
-    <row r="122" spans="2:21" ht="55.000000" customHeight="1">
+    <row r="122" spans="2:22" ht="55.000000" customHeight="1">
       <c r="B122" s="287" t="s">
         <v>68</v>
       </c>
       <c r="C122" s="288"/>
       <c r="D122" s="288"/>
       <c r="E122" s="288"/>
-      <c r="F122" s="289" t="s">
+      <c r="F122" s="554" t="s">
         <v>69</v>
       </c>
-      <c r="G122" s="290"/>
-      <c r="H122" s="290"/>
-      <c r="I122" s="290"/>
-      <c r="J122" s="290"/>
-      <c r="K122" s="290"/>
-      <c r="L122" s="290"/>
-      <c r="M122" s="290"/>
-      <c r="N122" s="290"/>
-      <c r="O122" s="290"/>
-      <c r="P122" s="290"/>
-      <c r="Q122" s="290"/>
-      <c r="R122" s="290"/>
-      <c r="S122" s="290"/>
-      <c r="T122" s="290"/>
-      <c r="U122" s="291"/>
-    </row>
-    <row r="123" spans="2:21" ht="55.000000" customHeight="1">
-      <c r="B123" s="260" t="s">
-        <v>70</v>
-      </c>
-      <c r="C123" s="261"/>
-      <c r="D123" s="261"/>
-      <c r="E123" s="261"/>
-      <c r="F123" s="264" t="s">
-        <v>71</v>
-      </c>
-      <c r="G123" s="265"/>
-      <c r="H123" s="265"/>
-      <c r="I123" s="265"/>
-      <c r="J123" s="265"/>
-      <c r="K123" s="265"/>
-      <c r="L123" s="265"/>
-      <c r="M123" s="265"/>
-      <c r="N123" s="265"/>
-      <c r="O123" s="265"/>
-      <c r="P123" s="265"/>
-      <c r="Q123" s="265"/>
-      <c r="R123" s="265"/>
-      <c r="S123" s="265"/>
-      <c r="T123" s="265"/>
-      <c r="U123" s="266"/>
-    </row>
-    <row r="124" spans="2:21" ht="55.000000" customHeight="1">
-      <c r="B124" s="260" t="s">
-        <v>72</v>
-      </c>
-      <c r="C124" s="261"/>
-      <c r="D124" s="261"/>
-      <c r="E124" s="261"/>
-      <c r="F124" s="264" t="s">
-        <v>73</v>
-      </c>
-      <c r="G124" s="265"/>
-      <c r="H124" s="265"/>
-      <c r="I124" s="265"/>
-      <c r="J124" s="265"/>
-      <c r="K124" s="265"/>
-      <c r="L124" s="265"/>
-      <c r="M124" s="265"/>
-      <c r="N124" s="265"/>
-      <c r="O124" s="265"/>
-      <c r="P124" s="265"/>
-      <c r="Q124" s="265"/>
-      <c r="R124" s="265"/>
-      <c r="S124" s="265"/>
-      <c r="T124" s="265"/>
-      <c r="U124" s="266"/>
-    </row>
-    <row r="125" spans="2:21" ht="55.000000" customHeight="1">
-      <c r="B125" s="260"/>
-      <c r="C125" s="261"/>
-      <c r="D125" s="261"/>
-      <c r="E125" s="261"/>
-      <c r="F125" s="264" t="s">
-        <v>74</v>
-      </c>
-      <c r="G125" s="265"/>
-      <c r="H125" s="265"/>
-      <c r="I125" s="265"/>
-      <c r="J125" s="265"/>
-      <c r="K125" s="265"/>
-      <c r="L125" s="265"/>
-      <c r="M125" s="265"/>
-      <c r="N125" s="265"/>
-      <c r="O125" s="265"/>
-      <c r="P125" s="265"/>
-      <c r="Q125" s="265"/>
-      <c r="R125" s="265"/>
-      <c r="S125" s="265"/>
-      <c r="T125" s="265"/>
-      <c r="U125" s="266"/>
-    </row>
-    <row r="126" spans="2:21" ht="55.000000" customHeight="1">
-      <c r="B126" s="260"/>
-      <c r="C126" s="261"/>
-      <c r="D126" s="261"/>
-      <c r="E126" s="261"/>
-      <c r="F126" s="264" t="s">
-        <v>75</v>
-      </c>
-      <c r="G126" s="265"/>
-      <c r="H126" s="265"/>
-      <c r="I126" s="265"/>
-      <c r="J126" s="265"/>
-      <c r="K126" s="265"/>
-      <c r="L126" s="265"/>
-      <c r="M126" s="265"/>
-      <c r="N126" s="265"/>
-      <c r="O126" s="265"/>
-      <c r="P126" s="265"/>
-      <c r="Q126" s="265"/>
-      <c r="R126" s="265"/>
-      <c r="S126" s="265"/>
-      <c r="T126" s="265"/>
-      <c r="U126" s="266"/>
-    </row>
-    <row r="127" spans="2:21" ht="55.000000" customHeight="1">
-      <c r="B127" s="260" t="s">
-        <v>76</v>
-      </c>
-      <c r="C127" s="261"/>
-      <c r="D127" s="261"/>
-      <c r="E127" s="261"/>
-      <c r="F127" s="277" t="s">
-        <v>297</v>
-      </c>
-      <c r="G127" s="278"/>
-      <c r="H127" s="278"/>
-      <c r="I127" s="278"/>
-      <c r="J127" s="278"/>
-      <c r="K127" s="278"/>
-      <c r="L127" s="278"/>
-      <c r="M127" s="278"/>
-      <c r="N127" s="278"/>
-      <c r="O127" s="278"/>
-      <c r="P127" s="278"/>
-      <c r="Q127" s="278"/>
-      <c r="R127" s="278"/>
-      <c r="S127" s="278"/>
-      <c r="T127" s="278"/>
-      <c r="U127" s="279"/>
-    </row>
-    <row r="128" spans="2:21" ht="55.000000" hidden="1" customHeight="1">
-      <c r="B128" s="260"/>
-      <c r="C128" s="261"/>
-      <c r="D128" s="261"/>
-      <c r="E128" s="261"/>
-      <c r="F128" s="280"/>
-      <c r="G128" s="281"/>
-      <c r="H128" s="281"/>
-      <c r="I128" s="281"/>
-      <c r="J128" s="281"/>
-      <c r="K128" s="281"/>
-      <c r="L128" s="281"/>
-      <c r="M128" s="281"/>
-      <c r="N128" s="281"/>
-      <c r="O128" s="281"/>
-      <c r="P128" s="281"/>
-      <c r="Q128" s="281"/>
-      <c r="R128" s="281"/>
-      <c r="S128" s="281"/>
-      <c r="T128" s="281"/>
-      <c r="U128" s="282"/>
-    </row>
-    <row r="129" spans="2:21" ht="55.000000" hidden="1" customHeight="1">
-      <c r="B129" s="260"/>
-      <c r="C129" s="261"/>
-      <c r="D129" s="261"/>
-      <c r="E129" s="261"/>
-      <c r="F129" s="283"/>
-      <c r="G129" s="284"/>
-      <c r="H129" s="284"/>
-      <c r="I129" s="284"/>
-      <c r="J129" s="284"/>
-      <c r="K129" s="284"/>
-      <c r="L129" s="284"/>
-      <c r="M129" s="284"/>
-      <c r="N129" s="284"/>
-      <c r="O129" s="284"/>
-      <c r="P129" s="284"/>
-      <c r="Q129" s="284"/>
-      <c r="R129" s="284"/>
-      <c r="S129" s="284"/>
-      <c r="T129" s="284"/>
-      <c r="U129" s="285"/>
-    </row>
-    <row r="130" spans="2:21" ht="55.000000" customHeight="1">
-      <c r="B130" s="260" t="s">
-        <v>77</v>
-      </c>
-      <c r="C130" s="261"/>
-      <c r="D130" s="286" t="s">
-        <v>78</v>
-      </c>
-      <c r="E130" s="286"/>
-      <c r="F130" s="264" t="s">
-        <v>298</v>
-      </c>
-      <c r="G130" s="265"/>
-      <c r="H130" s="265"/>
-      <c r="I130" s="265"/>
-      <c r="J130" s="265"/>
-      <c r="K130" s="265"/>
-      <c r="L130" s="265"/>
-      <c r="M130" s="265"/>
-      <c r="N130" s="265"/>
-      <c r="O130" s="265"/>
-      <c r="P130" s="265"/>
-      <c r="Q130" s="265"/>
-      <c r="R130" s="265"/>
-      <c r="S130" s="265"/>
-      <c r="T130" s="265"/>
-      <c r="U130" s="266"/>
-    </row>
-    <row r="131" spans="2:21" ht="55.000000" customHeight="1">
-      <c r="B131" s="260"/>
-      <c r="C131" s="261"/>
-      <c r="D131" s="286"/>
-      <c r="E131" s="286"/>
-      <c r="F131" s="264" t="s">
-        <v>299</v>
-      </c>
-      <c r="G131" s="265"/>
-      <c r="H131" s="265"/>
-      <c r="I131" s="265"/>
-      <c r="J131" s="265"/>
-      <c r="K131" s="265"/>
-      <c r="L131" s="265"/>
-      <c r="M131" s="265"/>
-      <c r="N131" s="265"/>
-      <c r="O131" s="265"/>
-      <c r="P131" s="265"/>
-      <c r="Q131" s="265"/>
-      <c r="R131" s="265"/>
-      <c r="S131" s="265"/>
-      <c r="T131" s="265"/>
-      <c r="U131" s="266"/>
-    </row>
-    <row r="132" spans="2:21" ht="55.000000" customHeight="1">
-      <c r="B132" s="260"/>
-      <c r="C132" s="261"/>
-      <c r="D132" s="286"/>
-      <c r="E132" s="286"/>
-      <c r="F132" s="264" t="s">
-        <v>75</v>
-      </c>
-      <c r="G132" s="265"/>
-      <c r="H132" s="265"/>
-      <c r="I132" s="265"/>
-      <c r="J132" s="265"/>
-      <c r="K132" s="265"/>
-      <c r="L132" s="265"/>
-      <c r="M132" s="265"/>
-      <c r="N132" s="265"/>
-      <c r="O132" s="265"/>
-      <c r="P132" s="265"/>
-      <c r="Q132" s="265"/>
-      <c r="R132" s="265"/>
-      <c r="S132" s="265"/>
-      <c r="T132" s="265"/>
-      <c r="U132" s="266"/>
-    </row>
-    <row r="133" spans="2:21" ht="55.000000" customHeight="1">
-      <c r="B133" s="260"/>
-      <c r="C133" s="261"/>
-      <c r="D133" s="286" t="s">
-        <v>79</v>
-      </c>
-      <c r="E133" s="286"/>
-      <c r="F133" s="277" t="s">
-        <v>300</v>
-      </c>
-      <c r="G133" s="278"/>
-      <c r="H133" s="278"/>
-      <c r="I133" s="278"/>
-      <c r="J133" s="278"/>
-      <c r="K133" s="278"/>
-      <c r="L133" s="278"/>
-      <c r="M133" s="278"/>
-      <c r="N133" s="278"/>
-      <c r="O133" s="278"/>
-      <c r="P133" s="278"/>
-      <c r="Q133" s="278"/>
-      <c r="R133" s="278"/>
-      <c r="S133" s="278"/>
-      <c r="T133" s="278"/>
-      <c r="U133" s="279"/>
-    </row>
-    <row r="134" spans="2:21" ht="55.000000" hidden="1" customHeight="1">
-      <c r="B134" s="260"/>
-      <c r="C134" s="261"/>
-      <c r="D134" s="286"/>
-      <c r="E134" s="286"/>
-      <c r="F134" s="280"/>
-      <c r="G134" s="281"/>
-      <c r="H134" s="281"/>
-      <c r="I134" s="281"/>
-      <c r="J134" s="281"/>
-      <c r="K134" s="281"/>
-      <c r="L134" s="281"/>
-      <c r="M134" s="281"/>
-      <c r="N134" s="281"/>
-      <c r="O134" s="281"/>
-      <c r="P134" s="281"/>
-      <c r="Q134" s="281"/>
-      <c r="R134" s="281"/>
-      <c r="S134" s="281"/>
-      <c r="T134" s="281"/>
-      <c r="U134" s="282"/>
-    </row>
-    <row r="135" spans="2:21" ht="55.000000" hidden="1" customHeight="1">
-      <c r="B135" s="260"/>
-      <c r="C135" s="261"/>
-      <c r="D135" s="286"/>
-      <c r="E135" s="286"/>
-      <c r="F135" s="283"/>
-      <c r="G135" s="284"/>
-      <c r="H135" s="284"/>
-      <c r="I135" s="284"/>
-      <c r="J135" s="284"/>
-      <c r="K135" s="284"/>
-      <c r="L135" s="284"/>
-      <c r="M135" s="284"/>
-      <c r="N135" s="284"/>
-      <c r="O135" s="284"/>
-      <c r="P135" s="284"/>
-      <c r="Q135" s="284"/>
-      <c r="R135" s="284"/>
-      <c r="S135" s="284"/>
-      <c r="T135" s="284"/>
-      <c r="U135" s="285"/>
-    </row>
-    <row r="136" spans="2:21" ht="55.000000" customHeight="1">
-      <c r="B136" s="260" t="s">
-        <v>80</v>
-      </c>
-      <c r="C136" s="261"/>
-      <c r="D136" s="261"/>
-      <c r="E136" s="261"/>
-      <c r="F136" s="264" t="s">
-        <v>73</v>
-      </c>
-      <c r="G136" s="265"/>
-      <c r="H136" s="265"/>
-      <c r="I136" s="265"/>
-      <c r="J136" s="265"/>
-      <c r="K136" s="265"/>
-      <c r="L136" s="265"/>
-      <c r="M136" s="265"/>
-      <c r="N136" s="265"/>
-      <c r="O136" s="265"/>
-      <c r="P136" s="265"/>
-      <c r="Q136" s="265"/>
-      <c r="R136" s="265"/>
-      <c r="S136" s="265"/>
-      <c r="T136" s="265"/>
-      <c r="U136" s="266"/>
-    </row>
-    <row r="137" spans="2:21" ht="55.000000" customHeight="1">
-      <c r="B137" s="260"/>
-      <c r="C137" s="261"/>
-      <c r="D137" s="261"/>
-      <c r="E137" s="261"/>
-      <c r="F137" s="264" t="s">
-        <v>74</v>
-      </c>
-      <c r="G137" s="265"/>
-      <c r="H137" s="265"/>
-      <c r="I137" s="265"/>
-      <c r="J137" s="265"/>
-      <c r="K137" s="265"/>
-      <c r="L137" s="265"/>
-      <c r="M137" s="265"/>
-      <c r="N137" s="265"/>
-      <c r="O137" s="265"/>
-      <c r="P137" s="265"/>
-      <c r="Q137" s="265"/>
-      <c r="R137" s="265"/>
-      <c r="S137" s="265"/>
-      <c r="T137" s="265"/>
-      <c r="U137" s="266"/>
-    </row>
-    <row r="138" spans="2:21" ht="55.000000" customHeight="1">
-      <c r="B138" s="262"/>
-      <c r="C138" s="263"/>
-      <c r="D138" s="263"/>
-      <c r="E138" s="263"/>
-      <c r="F138" s="267" t="s">
-        <v>75</v>
-      </c>
-      <c r="G138" s="268"/>
-      <c r="H138" s="268"/>
-      <c r="I138" s="268"/>
-      <c r="J138" s="268"/>
-      <c r="K138" s="268"/>
-      <c r="L138" s="268"/>
-      <c r="M138" s="268"/>
-      <c r="N138" s="268"/>
-      <c r="O138" s="268"/>
-      <c r="P138" s="268"/>
-      <c r="Q138" s="268"/>
-      <c r="R138" s="268"/>
-      <c r="S138" s="268"/>
-      <c r="T138" s="268"/>
-      <c r="U138" s="269"/>
-    </row>
-    <row r="139" spans="2:21" ht="16.500000" customHeight="1">
+      <c r="G122" s="552"/>
+      <c r="H122" s="552"/>
+      <c r="I122" s="552"/>
+      <c r="J122" s="552"/>
+      <c r="K122" s="552"/>
+      <c r="L122" s="552"/>
+      <c r="M122" s="552"/>
+      <c r="N122" s="649"/>
+      <c r="O122" s="653" t="s">
+        <v>464</v>
+      </c>
+      <c r="P122" s="552"/>
+      <c r="Q122" s="552"/>
+      <c r="R122" s="552"/>
+      <c r="S122" s="552"/>
+      <c r="T122" s="552"/>
+      <c r="U122" s="553"/>
+      <c r="V122" s="654"/>
+    </row>
+    <row r="123" spans="2:22" ht="55.000000" customHeight="1">
+      <c r="B123" s="674" t="s">
+        <v>478</v>
+      </c>
+      <c r="C123" s="675"/>
+      <c r="D123" s="675"/>
+      <c r="E123" s="676"/>
+      <c r="F123" s="677" t="s">
+        <v>477</v>
+      </c>
+      <c r="G123" s="678"/>
+      <c r="H123" s="678"/>
+      <c r="I123" s="678"/>
+      <c r="J123" s="678"/>
+      <c r="K123" s="678"/>
+      <c r="L123" s="678"/>
+      <c r="M123" s="678"/>
+      <c r="N123" s="678"/>
+      <c r="O123" s="655"/>
+      <c r="P123" s="589"/>
+      <c r="Q123" s="589"/>
+      <c r="R123" s="589"/>
+      <c r="S123" s="589"/>
+      <c r="T123" s="589"/>
+      <c r="U123" s="590"/>
+      <c r="V123" s="654"/>
+    </row>
+    <row r="124" spans="2:22" ht="55.000000" customHeight="1">
+      <c r="B124" s="679"/>
+      <c r="C124" s="680"/>
+      <c r="D124" s="680"/>
+      <c r="E124" s="681"/>
+      <c r="F124" s="682"/>
+      <c r="G124" s="683"/>
+      <c r="H124" s="683"/>
+      <c r="I124" s="683"/>
+      <c r="J124" s="683"/>
+      <c r="K124" s="683"/>
+      <c r="L124" s="683"/>
+      <c r="M124" s="683"/>
+      <c r="N124" s="683"/>
+      <c r="O124" s="656"/>
+      <c r="P124" s="612"/>
+      <c r="Q124" s="612"/>
+      <c r="R124" s="612"/>
+      <c r="S124" s="612"/>
+      <c r="T124" s="612"/>
+      <c r="U124" s="643"/>
+      <c r="V124" s="654"/>
+    </row>
+    <row r="125" spans="2:22" ht="55.000000" customHeight="1">
+      <c r="B125" s="684"/>
+      <c r="C125" s="685"/>
+      <c r="D125" s="685"/>
+      <c r="E125" s="686"/>
+      <c r="F125" s="687"/>
+      <c r="G125" s="688"/>
+      <c r="H125" s="688"/>
+      <c r="I125" s="688"/>
+      <c r="J125" s="688"/>
+      <c r="K125" s="688"/>
+      <c r="L125" s="688"/>
+      <c r="M125" s="688"/>
+      <c r="N125" s="688"/>
+      <c r="O125" s="657"/>
+      <c r="P125" s="616"/>
+      <c r="Q125" s="616"/>
+      <c r="R125" s="616"/>
+      <c r="S125" s="616"/>
+      <c r="T125" s="616"/>
+      <c r="U125" s="644"/>
+      <c r="V125" s="654"/>
+    </row>
+    <row r="126" spans="2:22" ht="55.000000" customHeight="1">
+      <c r="B126" s="608" t="s">
+        <v>453</v>
+      </c>
+      <c r="C126" s="589"/>
+      <c r="D126" s="589"/>
+      <c r="E126" s="620"/>
+      <c r="F126" s="677" t="s">
+        <v>480</v>
+      </c>
+      <c r="G126" s="678"/>
+      <c r="H126" s="678"/>
+      <c r="I126" s="678"/>
+      <c r="J126" s="678"/>
+      <c r="K126" s="678"/>
+      <c r="L126" s="678"/>
+      <c r="M126" s="678"/>
+      <c r="N126" s="678"/>
+      <c r="O126" s="655"/>
+      <c r="P126" s="589"/>
+      <c r="Q126" s="589"/>
+      <c r="R126" s="589"/>
+      <c r="S126" s="589"/>
+      <c r="T126" s="589"/>
+      <c r="U126" s="590"/>
+      <c r="V126" s="654"/>
+    </row>
+    <row r="127" spans="2:22" ht="55.000000" customHeight="1">
+      <c r="B127" s="611"/>
+      <c r="C127" s="612"/>
+      <c r="D127" s="612"/>
+      <c r="E127" s="621"/>
+      <c r="F127" s="682"/>
+      <c r="G127" s="683"/>
+      <c r="H127" s="683"/>
+      <c r="I127" s="683"/>
+      <c r="J127" s="683"/>
+      <c r="K127" s="683"/>
+      <c r="L127" s="683"/>
+      <c r="M127" s="683"/>
+      <c r="N127" s="683"/>
+      <c r="O127" s="656"/>
+      <c r="P127" s="612"/>
+      <c r="Q127" s="612"/>
+      <c r="R127" s="612"/>
+      <c r="S127" s="612"/>
+      <c r="T127" s="612"/>
+      <c r="U127" s="643"/>
+      <c r="V127" s="654"/>
+    </row>
+    <row r="128" spans="2:22" ht="55.000000" hidden="1" customHeight="1">
+      <c r="B128" s="611"/>
+      <c r="C128" s="612"/>
+      <c r="D128" s="612"/>
+      <c r="E128" s="621"/>
+      <c r="F128" s="682"/>
+      <c r="G128" s="683"/>
+      <c r="H128" s="683"/>
+      <c r="I128" s="683"/>
+      <c r="J128" s="683"/>
+      <c r="K128" s="683"/>
+      <c r="L128" s="683"/>
+      <c r="M128" s="683"/>
+      <c r="N128" s="683"/>
+      <c r="O128" s="656"/>
+      <c r="P128" s="612"/>
+      <c r="Q128" s="612"/>
+      <c r="R128" s="612"/>
+      <c r="S128" s="612"/>
+      <c r="T128" s="612"/>
+      <c r="U128" s="643"/>
+      <c r="V128" s="654"/>
+    </row>
+    <row r="129" spans="2:22" ht="55.000000" hidden="1" customHeight="1">
+      <c r="B129" s="611"/>
+      <c r="C129" s="612"/>
+      <c r="D129" s="612"/>
+      <c r="E129" s="621"/>
+      <c r="F129" s="682"/>
+      <c r="G129" s="683"/>
+      <c r="H129" s="683"/>
+      <c r="I129" s="683"/>
+      <c r="J129" s="683"/>
+      <c r="K129" s="683"/>
+      <c r="L129" s="683"/>
+      <c r="M129" s="683"/>
+      <c r="N129" s="683"/>
+      <c r="O129" s="656"/>
+      <c r="P129" s="612"/>
+      <c r="Q129" s="612"/>
+      <c r="R129" s="612"/>
+      <c r="S129" s="612"/>
+      <c r="T129" s="612"/>
+      <c r="U129" s="643"/>
+      <c r="V129" s="654"/>
+    </row>
+    <row r="130" spans="2:22" ht="55.000000" customHeight="1">
+      <c r="B130" s="615"/>
+      <c r="C130" s="616"/>
+      <c r="D130" s="617"/>
+      <c r="E130" s="618"/>
+      <c r="F130" s="687"/>
+      <c r="G130" s="688"/>
+      <c r="H130" s="688"/>
+      <c r="I130" s="688"/>
+      <c r="J130" s="688"/>
+      <c r="K130" s="688"/>
+      <c r="L130" s="688"/>
+      <c r="M130" s="688"/>
+      <c r="N130" s="688"/>
+      <c r="O130" s="657"/>
+      <c r="P130" s="616"/>
+      <c r="Q130" s="616"/>
+      <c r="R130" s="616"/>
+      <c r="S130" s="616"/>
+      <c r="T130" s="616"/>
+      <c r="U130" s="644"/>
+      <c r="V130" s="654"/>
+    </row>
+    <row r="131" spans="2:22" ht="55.000000" customHeight="1">
+      <c r="B131" s="608" t="s">
+        <v>265</v>
+      </c>
+      <c r="C131" s="589"/>
+      <c r="D131" s="609"/>
+      <c r="E131" s="610"/>
+      <c r="F131" s="677" t="s">
+        <v>481</v>
+      </c>
+      <c r="G131" s="678"/>
+      <c r="H131" s="678"/>
+      <c r="I131" s="678"/>
+      <c r="J131" s="678"/>
+      <c r="K131" s="678"/>
+      <c r="L131" s="678"/>
+      <c r="M131" s="678"/>
+      <c r="N131" s="678"/>
+      <c r="O131" s="655"/>
+      <c r="P131" s="589"/>
+      <c r="Q131" s="589"/>
+      <c r="R131" s="589"/>
+      <c r="S131" s="589"/>
+      <c r="T131" s="589"/>
+      <c r="U131" s="590"/>
+      <c r="V131" s="654"/>
+    </row>
+    <row r="132" spans="2:22" ht="55.000000" customHeight="1">
+      <c r="B132" s="615"/>
+      <c r="C132" s="616"/>
+      <c r="D132" s="617"/>
+      <c r="E132" s="618"/>
+      <c r="F132" s="687"/>
+      <c r="G132" s="688"/>
+      <c r="H132" s="688"/>
+      <c r="I132" s="688"/>
+      <c r="J132" s="688"/>
+      <c r="K132" s="688"/>
+      <c r="L132" s="688"/>
+      <c r="M132" s="688"/>
+      <c r="N132" s="688"/>
+      <c r="O132" s="657"/>
+      <c r="P132" s="616"/>
+      <c r="Q132" s="616"/>
+      <c r="R132" s="616"/>
+      <c r="S132" s="616"/>
+      <c r="T132" s="616"/>
+      <c r="U132" s="644"/>
+      <c r="V132" s="654"/>
+    </row>
+    <row r="133" spans="2:22" ht="55.000000" customHeight="1">
+      <c r="B133" s="661" t="s">
+        <v>454</v>
+      </c>
+      <c r="C133" s="662"/>
+      <c r="D133" s="662"/>
+      <c r="E133" s="663"/>
+      <c r="F133" s="629"/>
+      <c r="G133" s="630"/>
+      <c r="H133" s="630"/>
+      <c r="I133" s="630"/>
+      <c r="J133" s="630"/>
+      <c r="K133" s="630"/>
+      <c r="L133" s="630"/>
+      <c r="M133" s="630"/>
+      <c r="N133" s="630"/>
+      <c r="O133" s="655"/>
+      <c r="P133" s="589"/>
+      <c r="Q133" s="589"/>
+      <c r="R133" s="589"/>
+      <c r="S133" s="589"/>
+      <c r="T133" s="589"/>
+      <c r="U133" s="590"/>
+      <c r="V133" s="654"/>
+    </row>
+    <row r="134" spans="2:22" ht="55.000000" hidden="1" customHeight="1">
+      <c r="B134" s="664"/>
+      <c r="C134" s="665"/>
+      <c r="D134" s="665"/>
+      <c r="E134" s="666"/>
+      <c r="F134" s="632"/>
+      <c r="G134" s="633"/>
+      <c r="H134" s="633"/>
+      <c r="I134" s="633"/>
+      <c r="J134" s="633"/>
+      <c r="K134" s="633"/>
+      <c r="L134" s="633"/>
+      <c r="M134" s="633"/>
+      <c r="N134" s="632"/>
+      <c r="O134" s="658"/>
+      <c r="P134" s="625"/>
+      <c r="Q134" s="625"/>
+      <c r="R134" s="625"/>
+      <c r="S134" s="625"/>
+      <c r="T134" s="625"/>
+      <c r="U134" s="581"/>
+      <c r="V134" s="654"/>
+    </row>
+    <row r="135" spans="2:22" ht="55.000000" hidden="1" customHeight="1">
+      <c r="B135" s="667"/>
+      <c r="C135" s="668"/>
+      <c r="D135" s="668"/>
+      <c r="E135" s="669"/>
+      <c r="F135" s="635"/>
+      <c r="G135" s="636"/>
+      <c r="H135" s="636"/>
+      <c r="I135" s="636"/>
+      <c r="J135" s="636"/>
+      <c r="K135" s="636"/>
+      <c r="L135" s="636"/>
+      <c r="M135" s="636"/>
+      <c r="N135" s="635"/>
+      <c r="O135" s="659"/>
+      <c r="P135" s="583"/>
+      <c r="Q135" s="583"/>
+      <c r="R135" s="583"/>
+      <c r="S135" s="583"/>
+      <c r="T135" s="583"/>
+      <c r="U135" s="584"/>
+      <c r="V135" s="654"/>
+    </row>
+    <row r="136" spans="2:22" ht="55.000000" customHeight="1">
+      <c r="B136" s="602" t="s">
+        <v>455</v>
+      </c>
+      <c r="C136" s="586"/>
+      <c r="D136" s="586"/>
+      <c r="E136" s="603"/>
+      <c r="F136" s="670" t="s">
+        <v>476</v>
+      </c>
+      <c r="G136" s="671"/>
+      <c r="H136" s="671"/>
+      <c r="I136" s="671"/>
+      <c r="J136" s="671"/>
+      <c r="K136" s="671"/>
+      <c r="L136" s="671"/>
+      <c r="M136" s="671"/>
+      <c r="N136" s="671"/>
+      <c r="O136" s="660"/>
+      <c r="P136" s="586"/>
+      <c r="Q136" s="586"/>
+      <c r="R136" s="586"/>
+      <c r="S136" s="586"/>
+      <c r="T136" s="586"/>
+      <c r="U136" s="587"/>
+      <c r="V136" s="654"/>
+    </row>
+    <row r="137" spans="2:22" ht="55.000000" customHeight="1">
+      <c r="B137" s="602" t="s">
+        <v>457</v>
+      </c>
+      <c r="C137" s="586"/>
+      <c r="D137" s="586"/>
+      <c r="E137" s="603"/>
+      <c r="F137" s="670" t="s">
+        <v>475</v>
+      </c>
+      <c r="G137" s="671"/>
+      <c r="H137" s="671"/>
+      <c r="I137" s="671"/>
+      <c r="J137" s="671"/>
+      <c r="K137" s="671"/>
+      <c r="L137" s="671"/>
+      <c r="M137" s="671"/>
+      <c r="N137" s="671"/>
+      <c r="O137" s="660"/>
+      <c r="P137" s="586"/>
+      <c r="Q137" s="586"/>
+      <c r="R137" s="586"/>
+      <c r="S137" s="586"/>
+      <c r="T137" s="586"/>
+      <c r="U137" s="587"/>
+      <c r="V137" s="654"/>
+    </row>
+    <row r="138" spans="2:22" ht="55.000000" customHeight="1">
+      <c r="B138" s="604" t="s">
+        <v>458</v>
+      </c>
+      <c r="C138" s="592"/>
+      <c r="D138" s="592"/>
+      <c r="E138" s="605"/>
+      <c r="F138" s="672"/>
+      <c r="G138" s="673"/>
+      <c r="H138" s="673"/>
+      <c r="I138" s="673"/>
+      <c r="J138" s="673"/>
+      <c r="K138" s="673"/>
+      <c r="L138" s="673"/>
+      <c r="M138" s="673"/>
+      <c r="N138" s="673"/>
+      <c r="O138" s="656"/>
+      <c r="P138" s="612"/>
+      <c r="Q138" s="612"/>
+      <c r="R138" s="612"/>
+      <c r="S138" s="612"/>
+      <c r="T138" s="612"/>
+      <c r="U138" s="612"/>
+      <c r="V138" s="652"/>
+    </row>
+    <row r="139" spans="2:22" ht="16.500000" customHeight="1">
       <c r="B139" s="270" t="s">
         <v>81</v>
       </c>
@@ -39636,7 +40680,7 @@
       <c r="T139" s="270"/>
       <c r="U139" s="270"/>
     </row>
-    <row r="140" spans="2:21" ht="42.000000" customHeight="1">
+    <row r="140" spans="2:22" ht="42.000000" customHeight="1">
       <c r="B140" s="271" t="s">
         <v>82</v>
       </c>
@@ -39660,7 +40704,7 @@
       <c r="T140" s="271"/>
       <c r="U140" s="271"/>
     </row>
-    <row r="141" spans="2:21" ht="30.000000" customHeight="1">
+    <row r="141" spans="2:22" ht="30.000000" customHeight="1">
       <c r="B141" s="272" t="s">
         <v>13</v>
       </c>
@@ -39691,7 +40735,7 @@
       <c r="T141" s="275"/>
       <c r="U141" s="276"/>
     </row>
-    <row r="142" spans="2:21" ht="30.000000" customHeight="1">
+    <row r="142" spans="2:22" ht="30.000000" customHeight="1">
       <c r="B142" s="36"/>
       <c r="C142" s="37" t="s">
         <v>4</v>
@@ -39730,7 +40774,7 @@
       <c r="T142" s="234"/>
       <c r="U142" s="235"/>
     </row>
-    <row r="143" spans="2:21" ht="30.000000" customHeight="1">
+    <row r="143" spans="2:22" ht="30.000000" customHeight="1">
       <c r="B143" s="36"/>
       <c r="C143" s="37"/>
       <c r="F143" s="6" t="s">
@@ -39765,7 +40809,7 @@
       <c r="T143" s="234"/>
       <c r="U143" s="235"/>
     </row>
-    <row r="144" spans="2:21" ht="30.000000" customHeight="1">
+    <row r="144" spans="2:22" ht="30.000000" customHeight="1">
       <c r="B144" s="36"/>
       <c r="C144" s="37"/>
       <c r="F144" s="6" t="s">
@@ -40404,7 +41448,7 @@
     <row r="171" ht="24.950000" customHeight="1"/>
     <row r="172" ht="24.950000" customHeight="1"/>
   </sheetData>
-  <mergeCells count="211">
+  <mergeCells count="214">
     <mergeCell ref="B7:U7"/>
     <mergeCell ref="B8:U8"/>
     <mergeCell ref="B9:U9"/>
@@ -40519,26 +41563,29 @@
     <mergeCell ref="B120:I120"/>
     <mergeCell ref="B121:U121"/>
     <mergeCell ref="B122:E122"/>
-    <mergeCell ref="F122:U122"/>
-    <mergeCell ref="B123:E123"/>
-    <mergeCell ref="F123:U123"/>
-    <mergeCell ref="B124:E126"/>
-    <mergeCell ref="F124:U124"/>
-    <mergeCell ref="F125:U125"/>
-    <mergeCell ref="F126:U126"/>
-    <mergeCell ref="B127:E129"/>
-    <mergeCell ref="F127:U129"/>
-    <mergeCell ref="B130:C135"/>
-    <mergeCell ref="D130:E132"/>
-    <mergeCell ref="F130:U130"/>
-    <mergeCell ref="F131:U131"/>
-    <mergeCell ref="F132:U132"/>
-    <mergeCell ref="D133:E135"/>
-    <mergeCell ref="F133:U135"/>
-    <mergeCell ref="B136:E138"/>
-    <mergeCell ref="F136:U136"/>
-    <mergeCell ref="F137:U137"/>
-    <mergeCell ref="F138:U138"/>
+    <mergeCell ref="F122:N122"/>
+    <mergeCell ref="O122:U122"/>
+    <mergeCell ref="B123:E125"/>
+    <mergeCell ref="F123:N125"/>
+    <mergeCell ref="O123:U125"/>
+    <mergeCell ref="B126:E130"/>
+    <mergeCell ref="F126:N130"/>
+    <mergeCell ref="O126:U130"/>
+    <mergeCell ref="B131:E132"/>
+    <mergeCell ref="F131:N132"/>
+    <mergeCell ref="O131:U132"/>
+    <mergeCell ref="B133:E135"/>
+    <mergeCell ref="F133:N133"/>
+    <mergeCell ref="O133:U133"/>
+    <mergeCell ref="B136:E136"/>
+    <mergeCell ref="F136:N136"/>
+    <mergeCell ref="O136:U136"/>
+    <mergeCell ref="B137:E137"/>
+    <mergeCell ref="F137:N137"/>
+    <mergeCell ref="O137:U137"/>
+    <mergeCell ref="B138:E138"/>
+    <mergeCell ref="F138:N138"/>
+    <mergeCell ref="O138:V138"/>
     <mergeCell ref="B139:U139"/>
     <mergeCell ref="B140:U140"/>
     <mergeCell ref="B141:H141"/>

--- a/repair/back/doc/estimate/detail.xlsx
+++ b/repair/back/doc/estimate/detail.xlsx
@@ -381,7 +381,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="482">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="485">
   <si>
     <t>식</t>
   </si>
@@ -2700,6 +2700,25 @@
  ◦ 대상 시설물(부재)에 대한 상태평가
  ◦ 시설물 전체의 상대평가 결과에 대한 책임
      기술자의 소견(안전등급 지정)
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ◦ 정밀안전점검 보고서 작성 및 FMS 등록</t>
+  </si>
+  <si>
+    <t>&lt;붙임 3&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 
+ ◦ 기본시설물 또는 주요부재의 외관조사 및 외관조
+     사망도 작성
+     - 콘크리트 구조물 : 균열, 누수, 박리, 박락,
+        층분리, 백태, 철근노출 등
+     - 강재 구조물 : 균열, 도장상태, 부식상태 등
+ ◦ 간단한 현장 재료시험 등
+     - 콘크리트 비파괴 강도시험(반발강도시험)
+     - 콘크리트 중성화 시험
+     - 시험물(부재) 변위측정
 </t>
   </si>
 </sst>
@@ -2781,7 +2800,7 @@
     <numFmt numFmtId="245" formatCode="0_ "/>
     <numFmt numFmtId="246" formatCode="yyyy&quot;년&quot;\ m&quot;월&quot;\ d&quot;일&quot;;@"/>
   </numFmts>
-  <fonts count="180">
+  <fonts count="179">
     <font>
       <sz val="11.0"/>
       <name val="돋움"/>
@@ -3757,11 +3776,6 @@
       <name val="함초롬바탕"/>
       <color rgb="FF000000"/>
     </font>
-    <font>
-      <sz val="10.0"/>
-      <name val="돋움"/>
-      <color/>
-    </font>
   </fonts>
   <fills count="45">
     <fill>
@@ -4032,7 +4046,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="128">
+  <borders count="127">
     <border>
       <left/>
       <right/>
@@ -5408,13 +5422,6 @@
       </bottom>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color auto="1"/>
       </left>
@@ -15012,7 +15019,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="801">
+  <cellXfs count="757">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="3104">
       <alignment vertical="center"/>
@@ -16949,64 +16956,37 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="66" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="179" fillId="0" borderId="122" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="122" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="70" fillId="0" borderId="123" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="122" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="123" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="124" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="125" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="124" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="125" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="126" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="125" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="126" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="127" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="99" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="69" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="96" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="95" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="98" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -17076,33 +17056,6 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="96" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="distributed" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="99" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="distributed" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="69" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="distributed" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="96" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="distributed" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="distributed" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="distributed" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="95" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="distributed" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="98" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="distributed" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="distributed" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="distributed" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="90" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="distributed" wrapText="1"/>
     </xf>
@@ -17181,33 +17134,6 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="96" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="99" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="69" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="96" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="95" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="98" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="90" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
     </xf>
@@ -17247,33 +17173,6 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="96" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="99" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="69" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="96" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="95" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="98" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="90" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -17343,33 +17242,6 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="96" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="justify" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="99" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="justify" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="69" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="justify" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="96" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="justify" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="justify" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="justify" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="95" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="justify" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="98" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="justify" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="justify" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="justify" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="90" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="justify" wrapText="1"/>
     </xf>
@@ -17399,6 +17271,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="73" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="justify" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3168">
@@ -21062,13 +20937,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="_x206956912" descr="xl/media/image4.png">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="2" name="_x206956912" descr="xl/media/image4.png"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -37620,8 +37489,8 @@
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.30" footer="0.30"/>
   <pageSetup paperSize="9" scale="90" orientation="portrait"/>
   <colBreaks count="2" manualBreakCount="2">
+    <brk id="9" max="35" man="1"/>
     <brk id="9" max="1048575" man="1"/>
-    <brk id="9" max="35" man="1"/>
   </colBreaks>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -37632,7 +37501,7 @@
   <sheetPr>
     <tabColor rgb="92d050"/>
   </sheetPr>
-  <dimension ref="B1:AUT164"/>
+  <dimension ref="B1:AUT172"/>
   <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="13.500000"/>
   <cols>
     <col min="2" max="6" width="4.44944451" customWidth="1" outlineLevel="0"/>
@@ -40265,23 +40134,23 @@
       <c r="V122" s="654"/>
     </row>
     <row r="123" spans="2:22" ht="55.000000" customHeight="1">
-      <c r="B123" s="674" t="s">
+      <c r="B123" s="665" t="s">
         <v>478</v>
       </c>
-      <c r="C123" s="675"/>
-      <c r="D123" s="675"/>
-      <c r="E123" s="676"/>
-      <c r="F123" s="677" t="s">
+      <c r="C123" s="666"/>
+      <c r="D123" s="666"/>
+      <c r="E123" s="667"/>
+      <c r="F123" s="668" t="s">
         <v>477</v>
       </c>
-      <c r="G123" s="678"/>
-      <c r="H123" s="678"/>
-      <c r="I123" s="678"/>
-      <c r="J123" s="678"/>
-      <c r="K123" s="678"/>
-      <c r="L123" s="678"/>
-      <c r="M123" s="678"/>
-      <c r="N123" s="678"/>
+      <c r="G123" s="669"/>
+      <c r="H123" s="669"/>
+      <c r="I123" s="669"/>
+      <c r="J123" s="669"/>
+      <c r="K123" s="669"/>
+      <c r="L123" s="669"/>
+      <c r="M123" s="669"/>
+      <c r="N123" s="669"/>
       <c r="O123" s="655"/>
       <c r="P123" s="589"/>
       <c r="Q123" s="589"/>
@@ -40292,19 +40161,19 @@
       <c r="V123" s="654"/>
     </row>
     <row r="124" spans="2:22" ht="55.000000" customHeight="1">
-      <c r="B124" s="679"/>
-      <c r="C124" s="680"/>
-      <c r="D124" s="680"/>
-      <c r="E124" s="681"/>
-      <c r="F124" s="682"/>
-      <c r="G124" s="683"/>
-      <c r="H124" s="683"/>
-      <c r="I124" s="683"/>
-      <c r="J124" s="683"/>
-      <c r="K124" s="683"/>
-      <c r="L124" s="683"/>
-      <c r="M124" s="683"/>
-      <c r="N124" s="683"/>
+      <c r="B124" s="670"/>
+      <c r="C124" s="671"/>
+      <c r="D124" s="671"/>
+      <c r="E124" s="672"/>
+      <c r="F124" s="673"/>
+      <c r="G124" s="674"/>
+      <c r="H124" s="674"/>
+      <c r="I124" s="674"/>
+      <c r="J124" s="674"/>
+      <c r="K124" s="674"/>
+      <c r="L124" s="674"/>
+      <c r="M124" s="674"/>
+      <c r="N124" s="674"/>
       <c r="O124" s="656"/>
       <c r="P124" s="612"/>
       <c r="Q124" s="612"/>
@@ -40315,19 +40184,19 @@
       <c r="V124" s="654"/>
     </row>
     <row r="125" spans="2:22" ht="55.000000" customHeight="1">
-      <c r="B125" s="684"/>
-      <c r="C125" s="685"/>
-      <c r="D125" s="685"/>
-      <c r="E125" s="686"/>
-      <c r="F125" s="687"/>
-      <c r="G125" s="688"/>
-      <c r="H125" s="688"/>
-      <c r="I125" s="688"/>
-      <c r="J125" s="688"/>
-      <c r="K125" s="688"/>
-      <c r="L125" s="688"/>
-      <c r="M125" s="688"/>
-      <c r="N125" s="688"/>
+      <c r="B125" s="675"/>
+      <c r="C125" s="676"/>
+      <c r="D125" s="676"/>
+      <c r="E125" s="677"/>
+      <c r="F125" s="678"/>
+      <c r="G125" s="679"/>
+      <c r="H125" s="679"/>
+      <c r="I125" s="679"/>
+      <c r="J125" s="679"/>
+      <c r="K125" s="679"/>
+      <c r="L125" s="679"/>
+      <c r="M125" s="679"/>
+      <c r="N125" s="679"/>
       <c r="O125" s="657"/>
       <c r="P125" s="616"/>
       <c r="Q125" s="616"/>
@@ -40344,17 +40213,17 @@
       <c r="C126" s="589"/>
       <c r="D126" s="589"/>
       <c r="E126" s="620"/>
-      <c r="F126" s="677" t="s">
-        <v>480</v>
-      </c>
-      <c r="G126" s="678"/>
-      <c r="H126" s="678"/>
-      <c r="I126" s="678"/>
-      <c r="J126" s="678"/>
-      <c r="K126" s="678"/>
-      <c r="L126" s="678"/>
-      <c r="M126" s="678"/>
-      <c r="N126" s="678"/>
+      <c r="F126" s="668" t="s">
+        <v>484</v>
+      </c>
+      <c r="G126" s="669"/>
+      <c r="H126" s="669"/>
+      <c r="I126" s="669"/>
+      <c r="J126" s="669"/>
+      <c r="K126" s="669"/>
+      <c r="L126" s="669"/>
+      <c r="M126" s="669"/>
+      <c r="N126" s="669"/>
       <c r="O126" s="655"/>
       <c r="P126" s="589"/>
       <c r="Q126" s="589"/>
@@ -40369,15 +40238,15 @@
       <c r="C127" s="612"/>
       <c r="D127" s="612"/>
       <c r="E127" s="621"/>
-      <c r="F127" s="682"/>
-      <c r="G127" s="683"/>
-      <c r="H127" s="683"/>
-      <c r="I127" s="683"/>
-      <c r="J127" s="683"/>
-      <c r="K127" s="683"/>
-      <c r="L127" s="683"/>
-      <c r="M127" s="683"/>
-      <c r="N127" s="683"/>
+      <c r="F127" s="673"/>
+      <c r="G127" s="674"/>
+      <c r="H127" s="674"/>
+      <c r="I127" s="674"/>
+      <c r="J127" s="674"/>
+      <c r="K127" s="674"/>
+      <c r="L127" s="674"/>
+      <c r="M127" s="674"/>
+      <c r="N127" s="674"/>
       <c r="O127" s="656"/>
       <c r="P127" s="612"/>
       <c r="Q127" s="612"/>
@@ -40392,15 +40261,15 @@
       <c r="C128" s="612"/>
       <c r="D128" s="612"/>
       <c r="E128" s="621"/>
-      <c r="F128" s="682"/>
-      <c r="G128" s="683"/>
-      <c r="H128" s="683"/>
-      <c r="I128" s="683"/>
-      <c r="J128" s="683"/>
-      <c r="K128" s="683"/>
-      <c r="L128" s="683"/>
-      <c r="M128" s="683"/>
-      <c r="N128" s="683"/>
+      <c r="F128" s="673"/>
+      <c r="G128" s="674"/>
+      <c r="H128" s="674"/>
+      <c r="I128" s="674"/>
+      <c r="J128" s="674"/>
+      <c r="K128" s="674"/>
+      <c r="L128" s="674"/>
+      <c r="M128" s="674"/>
+      <c r="N128" s="674"/>
       <c r="O128" s="656"/>
       <c r="P128" s="612"/>
       <c r="Q128" s="612"/>
@@ -40415,15 +40284,15 @@
       <c r="C129" s="612"/>
       <c r="D129" s="612"/>
       <c r="E129" s="621"/>
-      <c r="F129" s="682"/>
-      <c r="G129" s="683"/>
-      <c r="H129" s="683"/>
-      <c r="I129" s="683"/>
-      <c r="J129" s="683"/>
-      <c r="K129" s="683"/>
-      <c r="L129" s="683"/>
-      <c r="M129" s="683"/>
-      <c r="N129" s="683"/>
+      <c r="F129" s="673"/>
+      <c r="G129" s="674"/>
+      <c r="H129" s="674"/>
+      <c r="I129" s="674"/>
+      <c r="J129" s="674"/>
+      <c r="K129" s="674"/>
+      <c r="L129" s="674"/>
+      <c r="M129" s="674"/>
+      <c r="N129" s="674"/>
       <c r="O129" s="656"/>
       <c r="P129" s="612"/>
       <c r="Q129" s="612"/>
@@ -40438,15 +40307,15 @@
       <c r="C130" s="616"/>
       <c r="D130" s="617"/>
       <c r="E130" s="618"/>
-      <c r="F130" s="687"/>
-      <c r="G130" s="688"/>
-      <c r="H130" s="688"/>
-      <c r="I130" s="688"/>
-      <c r="J130" s="688"/>
-      <c r="K130" s="688"/>
-      <c r="L130" s="688"/>
-      <c r="M130" s="688"/>
-      <c r="N130" s="688"/>
+      <c r="F130" s="678"/>
+      <c r="G130" s="679"/>
+      <c r="H130" s="679"/>
+      <c r="I130" s="679"/>
+      <c r="J130" s="679"/>
+      <c r="K130" s="679"/>
+      <c r="L130" s="679"/>
+      <c r="M130" s="679"/>
+      <c r="N130" s="679"/>
       <c r="O130" s="657"/>
       <c r="P130" s="616"/>
       <c r="Q130" s="616"/>
@@ -40463,17 +40332,17 @@
       <c r="C131" s="589"/>
       <c r="D131" s="609"/>
       <c r="E131" s="610"/>
-      <c r="F131" s="677" t="s">
+      <c r="F131" s="668" t="s">
         <v>481</v>
       </c>
-      <c r="G131" s="678"/>
-      <c r="H131" s="678"/>
-      <c r="I131" s="678"/>
-      <c r="J131" s="678"/>
-      <c r="K131" s="678"/>
-      <c r="L131" s="678"/>
-      <c r="M131" s="678"/>
-      <c r="N131" s="678"/>
+      <c r="G131" s="669"/>
+      <c r="H131" s="669"/>
+      <c r="I131" s="669"/>
+      <c r="J131" s="669"/>
+      <c r="K131" s="669"/>
+      <c r="L131" s="669"/>
+      <c r="M131" s="669"/>
+      <c r="N131" s="669"/>
       <c r="O131" s="655"/>
       <c r="P131" s="589"/>
       <c r="Q131" s="589"/>
@@ -40488,15 +40357,15 @@
       <c r="C132" s="616"/>
       <c r="D132" s="617"/>
       <c r="E132" s="618"/>
-      <c r="F132" s="687"/>
-      <c r="G132" s="688"/>
-      <c r="H132" s="688"/>
-      <c r="I132" s="688"/>
-      <c r="J132" s="688"/>
-      <c r="K132" s="688"/>
-      <c r="L132" s="688"/>
-      <c r="M132" s="688"/>
-      <c r="N132" s="688"/>
+      <c r="F132" s="678"/>
+      <c r="G132" s="679"/>
+      <c r="H132" s="679"/>
+      <c r="I132" s="679"/>
+      <c r="J132" s="679"/>
+      <c r="K132" s="679"/>
+      <c r="L132" s="679"/>
+      <c r="M132" s="679"/>
+      <c r="N132" s="679"/>
       <c r="O132" s="657"/>
       <c r="P132" s="616"/>
       <c r="Q132" s="616"/>
@@ -40506,13 +40375,13 @@
       <c r="U132" s="644"/>
       <c r="V132" s="654"/>
     </row>
-    <row r="133" spans="2:22" ht="55.000000" customHeight="1">
-      <c r="B133" s="661" t="s">
+    <row r="133" spans="2:22" ht="55.000000" hidden="1" customHeight="1">
+      <c r="B133" s="608" t="s">
         <v>454</v>
       </c>
-      <c r="C133" s="662"/>
-      <c r="D133" s="662"/>
-      <c r="E133" s="663"/>
+      <c r="C133" s="589"/>
+      <c r="D133" s="589"/>
+      <c r="E133" s="620"/>
       <c r="F133" s="629"/>
       <c r="G133" s="630"/>
       <c r="H133" s="630"/>
@@ -40532,10 +40401,10 @@
       <c r="V133" s="654"/>
     </row>
     <row r="134" spans="2:22" ht="55.000000" hidden="1" customHeight="1">
-      <c r="B134" s="664"/>
-      <c r="C134" s="665"/>
-      <c r="D134" s="665"/>
-      <c r="E134" s="666"/>
+      <c r="B134" s="611"/>
+      <c r="C134" s="612"/>
+      <c r="D134" s="612"/>
+      <c r="E134" s="621"/>
       <c r="F134" s="632"/>
       <c r="G134" s="633"/>
       <c r="H134" s="633"/>
@@ -40555,10 +40424,10 @@
       <c r="V134" s="654"/>
     </row>
     <row r="135" spans="2:22" ht="55.000000" hidden="1" customHeight="1">
-      <c r="B135" s="667"/>
-      <c r="C135" s="668"/>
-      <c r="D135" s="668"/>
-      <c r="E135" s="669"/>
+      <c r="B135" s="615"/>
+      <c r="C135" s="616"/>
+      <c r="D135" s="616"/>
+      <c r="E135" s="622"/>
       <c r="F135" s="635"/>
       <c r="G135" s="636"/>
       <c r="H135" s="636"/>
@@ -40584,17 +40453,17 @@
       <c r="C136" s="586"/>
       <c r="D136" s="586"/>
       <c r="E136" s="603"/>
-      <c r="F136" s="670" t="s">
+      <c r="F136" s="661" t="s">
         <v>476</v>
       </c>
-      <c r="G136" s="671"/>
-      <c r="H136" s="671"/>
-      <c r="I136" s="671"/>
-      <c r="J136" s="671"/>
-      <c r="K136" s="671"/>
-      <c r="L136" s="671"/>
-      <c r="M136" s="671"/>
-      <c r="N136" s="671"/>
+      <c r="G136" s="662"/>
+      <c r="H136" s="662"/>
+      <c r="I136" s="662"/>
+      <c r="J136" s="662"/>
+      <c r="K136" s="662"/>
+      <c r="L136" s="662"/>
+      <c r="M136" s="662"/>
+      <c r="N136" s="662"/>
       <c r="O136" s="660"/>
       <c r="P136" s="586"/>
       <c r="Q136" s="586"/>
@@ -40611,17 +40480,17 @@
       <c r="C137" s="586"/>
       <c r="D137" s="586"/>
       <c r="E137" s="603"/>
-      <c r="F137" s="670" t="s">
+      <c r="F137" s="661" t="s">
         <v>475</v>
       </c>
-      <c r="G137" s="671"/>
-      <c r="H137" s="671"/>
-      <c r="I137" s="671"/>
-      <c r="J137" s="671"/>
-      <c r="K137" s="671"/>
-      <c r="L137" s="671"/>
-      <c r="M137" s="671"/>
-      <c r="N137" s="671"/>
+      <c r="G137" s="662"/>
+      <c r="H137" s="662"/>
+      <c r="I137" s="662"/>
+      <c r="J137" s="662"/>
+      <c r="K137" s="662"/>
+      <c r="L137" s="662"/>
+      <c r="M137" s="662"/>
+      <c r="N137" s="662"/>
       <c r="O137" s="660"/>
       <c r="P137" s="586"/>
       <c r="Q137" s="586"/>
@@ -40638,23 +40507,25 @@
       <c r="C138" s="592"/>
       <c r="D138" s="592"/>
       <c r="E138" s="605"/>
-      <c r="F138" s="672"/>
-      <c r="G138" s="673"/>
-      <c r="H138" s="673"/>
-      <c r="I138" s="673"/>
-      <c r="J138" s="673"/>
-      <c r="K138" s="673"/>
-      <c r="L138" s="673"/>
-      <c r="M138" s="673"/>
-      <c r="N138" s="673"/>
-      <c r="O138" s="656"/>
-      <c r="P138" s="612"/>
-      <c r="Q138" s="612"/>
-      <c r="R138" s="612"/>
-      <c r="S138" s="612"/>
-      <c r="T138" s="612"/>
-      <c r="U138" s="612"/>
-      <c r="V138" s="652"/>
+      <c r="F138" s="663" t="s">
+        <v>482</v>
+      </c>
+      <c r="G138" s="664"/>
+      <c r="H138" s="664"/>
+      <c r="I138" s="664"/>
+      <c r="J138" s="664"/>
+      <c r="K138" s="664"/>
+      <c r="L138" s="664"/>
+      <c r="M138" s="664"/>
+      <c r="N138" s="664"/>
+      <c r="O138" s="585"/>
+      <c r="P138" s="586"/>
+      <c r="Q138" s="586"/>
+      <c r="R138" s="586"/>
+      <c r="S138" s="586"/>
+      <c r="T138" s="586"/>
+      <c r="U138" s="603"/>
+      <c r="V138" s="625"/>
     </row>
     <row r="139" spans="2:22" ht="16.500000" customHeight="1">
       <c r="B139" s="270" t="s">
@@ -40743,7 +40614,7 @@
       <c r="D142" s="37"/>
       <c r="E142" s="37"/>
       <c r="F142" s="6" t="s">
-        <v>92</v>
+        <v>130</v>
       </c>
       <c r="G142" s="6"/>
       <c r="H142" s="6"/>
@@ -40755,7 +40626,7 @@
       <c r="K142" s="252"/>
       <c r="L142" s="252"/>
       <c r="M142" s="6" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="N142" s="6"/>
       <c r="O142" s="6" t="s">
@@ -40778,7 +40649,7 @@
       <c r="B143" s="36"/>
       <c r="C143" s="37"/>
       <c r="F143" s="6" t="s">
-        <v>93</v>
+        <v>132</v>
       </c>
       <c r="G143" s="6"/>
       <c r="H143" s="6"/>
@@ -40790,7 +40661,7 @@
       <c r="K143" s="252"/>
       <c r="L143" s="252"/>
       <c r="M143" s="6" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="N143" s="6"/>
       <c r="O143" s="6" t="s">
@@ -40813,7 +40684,7 @@
       <c r="B144" s="36"/>
       <c r="C144" s="37"/>
       <c r="F144" s="6" t="s">
-        <v>94</v>
+        <v>133</v>
       </c>
       <c r="G144" s="6"/>
       <c r="H144" s="6"/>
@@ -40848,7 +40719,7 @@
       <c r="B145" s="36"/>
       <c r="C145" s="37"/>
       <c r="F145" s="6" t="s">
-        <v>95</v>
+        <v>134</v>
       </c>
       <c r="G145" s="6"/>
       <c r="H145" s="6"/>
@@ -40887,7 +40758,7 @@
       <c r="D146" s="256"/>
       <c r="E146" s="256"/>
       <c r="F146" s="39" t="s">
-        <v>92</v>
+        <v>130</v>
       </c>
       <c r="G146" s="39"/>
       <c r="H146" s="39"/>
@@ -40922,7 +40793,7 @@
       <c r="B147" s="36"/>
       <c r="C147" s="37"/>
       <c r="F147" s="6" t="s">
-        <v>93</v>
+        <v>132</v>
       </c>
       <c r="G147" s="6"/>
       <c r="H147" s="6"/>
@@ -40957,7 +40828,7 @@
       <c r="B148" s="36"/>
       <c r="C148" s="37"/>
       <c r="F148" s="6" t="s">
-        <v>94</v>
+        <v>133</v>
       </c>
       <c r="G148" s="6"/>
       <c r="H148" s="6"/>
@@ -40994,7 +40865,7 @@
       <c r="D149" s="43"/>
       <c r="E149" s="43"/>
       <c r="F149" s="44" t="s">
-        <v>95</v>
+        <v>134</v>
       </c>
       <c r="G149" s="44"/>
       <c r="H149" s="44"/>
@@ -41027,7 +40898,7 @@
     </row>
     <row r="150" spans="2:24" ht="30.000000" customHeight="1">
       <c r="B150" s="243" t="s">
-        <v>1</v>
+        <v>135</v>
       </c>
       <c r="C150" s="244"/>
       <c r="D150" s="244"/>
@@ -41042,7 +40913,7 @@
       <c r="K150" s="46"/>
       <c r="L150" s="46"/>
       <c r="M150" s="245" t="s">
-        <v>12</v>
+        <v>136</v>
       </c>
       <c r="N150" s="245"/>
       <c r="O150" s="47"/>
@@ -41061,7 +40932,7 @@
     </row>
     <row r="151" spans="2:24" ht="30.000000" customHeight="1">
       <c r="B151" s="236" t="s">
-        <v>2</v>
+        <v>137</v>
       </c>
       <c r="C151" s="237"/>
       <c r="D151" s="237"/>
@@ -41076,7 +40947,7 @@
       <c r="K151" s="248"/>
       <c r="L151" s="248"/>
       <c r="M151" s="249" t="s">
-        <v>12</v>
+        <v>136</v>
       </c>
       <c r="N151" s="249"/>
       <c r="O151" s="48"/>
@@ -41095,7 +40966,7 @@
     </row>
     <row r="152" spans="2:24" ht="30.000000" customHeight="1">
       <c r="B152" s="243" t="s">
-        <v>3</v>
+        <v>138</v>
       </c>
       <c r="C152" s="244"/>
       <c r="D152" s="244"/>
@@ -41122,7 +40993,7 @@
     </row>
     <row r="153" spans="2:24" ht="30.000000" customHeight="1">
       <c r="B153" s="51" t="s">
-        <v>6</v>
+        <v>139</v>
       </c>
       <c r="C153" s="2"/>
       <c r="I153" s="50"/>
@@ -41144,7 +41015,7 @@
     </row>
     <row r="154" spans="2:24" ht="30.000000" customHeight="1">
       <c r="B154" s="51" t="s">
-        <v>7</v>
+        <v>140</v>
       </c>
       <c r="C154" s="2"/>
       <c r="I154" s="242">
@@ -41154,7 +41025,7 @@
       <c r="K154" s="242"/>
       <c r="L154" s="242"/>
       <c r="M154" s="6" t="s">
-        <v>0</v>
+        <v>146</v>
       </c>
       <c r="N154" s="6"/>
       <c r="O154" s="6" t="s">
@@ -41175,7 +41046,7 @@
     </row>
     <row r="155" spans="2:24" ht="30.000000" customHeight="1">
       <c r="B155" s="51" t="s">
-        <v>8</v>
+        <v>141</v>
       </c>
       <c r="C155" s="2"/>
       <c r="I155" s="242">
@@ -41185,7 +41056,7 @@
       <c r="K155" s="242"/>
       <c r="L155" s="242"/>
       <c r="M155" s="6" t="s">
-        <v>0</v>
+        <v>146</v>
       </c>
       <c r="N155" s="6"/>
       <c r="O155" s="6" t="s">
@@ -41206,7 +41077,7 @@
     </row>
     <row r="156" spans="2:24" ht="30.000000" customHeight="1">
       <c r="B156" s="51" t="s">
-        <v>9</v>
+        <v>142</v>
       </c>
       <c r="C156" s="6"/>
       <c r="I156" s="6" t="s">
@@ -41230,7 +41101,7 @@
     </row>
     <row r="157" spans="2:24" ht="30.000000" customHeight="1">
       <c r="B157" s="51" t="s">
-        <v>10</v>
+        <v>144</v>
       </c>
       <c r="C157" s="6"/>
       <c r="I157" s="6" t="s">
@@ -41254,7 +41125,7 @@
     </row>
     <row r="158" spans="2:24" ht="30.000000" customHeight="1">
       <c r="B158" s="51" t="s">
-        <v>11</v>
+        <v>145</v>
       </c>
       <c r="C158" s="6"/>
       <c r="I158" s="6"/>
@@ -41316,7 +41187,7 @@
       <c r="J160" s="48"/>
       <c r="K160" s="55"/>
       <c r="L160" s="49" t="s">
-        <v>14</v>
+        <v>149</v>
       </c>
       <c r="M160" s="49"/>
       <c r="N160" s="49"/>
@@ -41334,7 +41205,7 @@
     </row>
     <row r="161" spans="2:21" ht="30.000000" customHeight="1">
       <c r="B161" s="223" t="s">
-        <v>96</v>
+        <v>150</v>
       </c>
       <c r="C161" s="56"/>
       <c r="D161" s="56"/>
@@ -41361,7 +41232,7 @@
     </row>
     <row r="162" spans="2:21" ht="30.000000" customHeight="1">
       <c r="B162" s="223" t="s">
-        <v>97</v>
+        <v>151</v>
       </c>
       <c r="C162" s="56"/>
       <c r="D162" s="56"/>
@@ -41388,7 +41259,7 @@
     </row>
     <row r="163" spans="2:21" ht="30.000000" customHeight="1">
       <c r="B163" s="223" t="s">
-        <v>98</v>
+        <v>152</v>
       </c>
       <c r="C163" s="56"/>
       <c r="D163" s="56"/>
@@ -41585,7 +41456,7 @@
     <mergeCell ref="O137:U137"/>
     <mergeCell ref="B138:E138"/>
     <mergeCell ref="F138:N138"/>
-    <mergeCell ref="O138:V138"/>
+    <mergeCell ref="O138:U138"/>
     <mergeCell ref="B139:U139"/>
     <mergeCell ref="B140:U140"/>
     <mergeCell ref="B141:H141"/>

--- a/repair/back/doc/estimate/detail.xlsx
+++ b/repair/back/doc/estimate/detail.xlsx
@@ -40518,13 +40518,13 @@
       <c r="L138" s="664"/>
       <c r="M138" s="664"/>
       <c r="N138" s="664"/>
-      <c r="O138" s="585"/>
-      <c r="P138" s="586"/>
-      <c r="Q138" s="586"/>
-      <c r="R138" s="586"/>
-      <c r="S138" s="586"/>
-      <c r="T138" s="586"/>
-      <c r="U138" s="603"/>
+      <c r="O138" s="591"/>
+      <c r="P138" s="592"/>
+      <c r="Q138" s="592"/>
+      <c r="R138" s="592"/>
+      <c r="S138" s="592"/>
+      <c r="T138" s="592"/>
+      <c r="U138" s="605"/>
       <c r="V138" s="625"/>
     </row>
     <row r="139" spans="2:22" ht="16.500000" customHeight="1">
